--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_KESELURUHAN USAHA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_KESELURUHAN USAHA.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,217 +417,217 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Nama PCL</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Email PCL</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nama PML</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Email PML</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>nama_kec</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>koseka</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>USAHA - Ditemukan</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>USAHA - Baru</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>USAHA - subtotal</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - Ditemukan​</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - Baru​</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - subtotal​</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Total Usaha</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>APPROVED BY Pengawas</t>
         </is>
@@ -701,13 +689,13 @@
         <v>262</v>
       </c>
       <c r="O2" t="n">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="P2" t="n">
-        <v>260</v>
+        <v>302</v>
       </c>
       <c r="Q2" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>3</v>
@@ -716,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -725,31 +713,31 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="Z2" t="n">
-        <v>343</v>
+        <v>393</v>
       </c>
       <c r="AA2" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="AB2" t="n">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="AC2" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -761,16 +749,16 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="AL2" t="n">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="AM2" t="n">
         <v>364</v>
@@ -987,10 +975,10 @@
         <v>55</v>
       </c>
       <c r="O4" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="P4" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -999,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1011,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -1020,13 +1008,13 @@
         <v>429</v>
       </c>
       <c r="Z4" t="n">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="AA4" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="AB4" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1035,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1047,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
@@ -1056,7 +1044,7 @@
         <v>429</v>
       </c>
       <c r="AL4" t="n">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="AM4" t="n">
         <v>363</v>
@@ -1133,7 +1121,7 @@
         <v>219</v>
       </c>
       <c r="P5" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1154,10 +1142,10 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
         <v>425</v>
@@ -1169,7 +1157,7 @@
         <v>219</v>
       </c>
       <c r="AB5" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1190,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK5" t="n">
         <v>425</v>
@@ -1273,16 +1261,16 @@
         <v>28</v>
       </c>
       <c r="O6" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="P6" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1297,28 +1285,28 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Z6" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="AA6" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AB6" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1333,16 +1321,16 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AL6" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="AM6" t="n">
         <v>354</v>
@@ -1416,13 +1404,13 @@
         <v>227</v>
       </c>
       <c r="O7" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="P7" t="n">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1446,19 +1434,19 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Z7" t="n">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="AA7" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="AB7" t="n">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1482,10 +1470,10 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AL7" t="n">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="AM7" t="n">
         <v>336</v>
@@ -1559,16 +1547,16 @@
         <v>128</v>
       </c>
       <c r="O8" t="n">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="P8" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="R8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1589,22 +1577,22 @@
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="Z8" t="n">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="AA8" t="n">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="AB8" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="AD8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1625,10 +1613,10 @@
         <v>1</v>
       </c>
       <c r="AK8" t="n">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="AL8" t="n">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="AM8" t="n">
         <v>304</v>
@@ -1702,13 +1690,13 @@
         <v>236</v>
       </c>
       <c r="O9" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="P9" t="n">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1732,19 +1720,19 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Z9" t="n">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="AA9" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="AB9" t="n">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="AC9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1768,10 +1756,10 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AL9" t="n">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="AM9" t="n">
         <v>288</v>
@@ -1848,16 +1836,16 @@
         <v>186</v>
       </c>
       <c r="P10" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>7</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1884,16 +1872,16 @@
         <v>186</v>
       </c>
       <c r="AB10" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="AC10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>7</v>
       </c>
       <c r="AE10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1988,19 +1976,19 @@
         <v>107</v>
       </c>
       <c r="O11" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="P11" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -2012,31 +2000,31 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>407</v>
       </c>
       <c r="Z11" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="AA11" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="AB11" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="AC11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -2048,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>407</v>
       </c>
       <c r="AL11" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="AM11" t="n">
         <v>373</v>
@@ -2131,13 +2119,13 @@
         <v>195</v>
       </c>
       <c r="O12" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="P12" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -2155,25 +2143,25 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="Z12" t="n">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AA12" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AB12" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="AC12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
@@ -2191,16 +2179,16 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="AL12" t="n">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AM12" t="n">
         <v>383</v>
@@ -2274,13 +2262,13 @@
         <v>340</v>
       </c>
       <c r="O13" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P13" t="n">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2304,19 +2292,19 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="Z13" t="n">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="AA13" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="AB13" t="n">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="AC13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2340,10 +2328,10 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AL13" t="n">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="AM13" t="n">
         <v>373</v>
@@ -2417,16 +2405,16 @@
         <v>173</v>
       </c>
       <c r="O14" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="P14" t="n">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="Q14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -2450,19 +2438,19 @@
         <v>426</v>
       </c>
       <c r="Z14" t="n">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="AA14" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="AB14" t="n">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="AC14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AD14" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2486,7 +2474,7 @@
         <v>426</v>
       </c>
       <c r="AL14" t="n">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="AM14" t="n">
         <v>364</v>
@@ -2560,13 +2548,13 @@
         <v>296</v>
       </c>
       <c r="O15" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="P15" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="Q15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -2584,25 +2572,25 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Z15" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="AA15" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="AB15" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="AC15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AD15" t="n">
         <v>1</v>
@@ -2620,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AL15" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="AM15" t="n">
         <v>324</v>
@@ -2703,13 +2691,13 @@
         <v>113</v>
       </c>
       <c r="O16" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="P16" t="n">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="Q16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2718,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2730,22 +2718,22 @@
         <v>30</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="Z16" t="n">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="AA16" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB16" t="n">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="AC16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2754,7 +2742,7 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -2766,13 +2754,13 @@
         <v>30</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK16" t="n">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="AL16" t="n">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="AM16" t="n">
         <v>288</v>
@@ -2846,25 +2834,25 @@
         <v>88</v>
       </c>
       <c r="O17" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="P17" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2876,31 +2864,31 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="Z17" t="n">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="AA17" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AB17" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
@@ -2912,10 +2900,10 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AL17" t="n">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="AM17" t="n">
         <v>370</v>
@@ -2989,19 +2977,19 @@
         <v>223</v>
       </c>
       <c r="O18" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="P18" t="n">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="Q18" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="R18" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -3019,25 +3007,25 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="Z18" t="n">
-        <v>311</v>
+        <v>350</v>
       </c>
       <c r="AA18" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AB18" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="AC18" t="n">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="AD18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE18" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -3055,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL18" t="n">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AM18" t="n">
         <v>366</v>
@@ -3132,13 +3120,13 @@
         <v>145</v>
       </c>
       <c r="O19" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P19" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="Q19" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -3165,16 +3153,16 @@
         <v>454</v>
       </c>
       <c r="Z19" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AA19" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AB19" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="AC19" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3201,7 +3189,7 @@
         <v>454</v>
       </c>
       <c r="AL19" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM19" t="n">
         <v>423</v>
@@ -3421,10 +3409,10 @@
         <v>186</v>
       </c>
       <c r="P21" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>2</v>
@@ -3442,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -3457,10 +3445,10 @@
         <v>186</v>
       </c>
       <c r="AB21" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="AC21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>2</v>
@@ -3478,7 +3466,7 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
@@ -3561,16 +3549,16 @@
         <v>74</v>
       </c>
       <c r="O22" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="P22" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="S22" t="n">
         <v>7</v>
@@ -3591,22 +3579,22 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="Z22" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AA22" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AB22" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD22" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AE22" t="n">
         <v>7</v>
@@ -3627,10 +3615,10 @@
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AL22" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AM22" t="n">
         <v>410</v>
@@ -3704,19 +3692,19 @@
         <v>92</v>
       </c>
       <c r="O23" t="n">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="P23" t="n">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -3734,25 +3722,25 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="Z23" t="n">
+        <v>313</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>220</v>
+      </c>
+      <c r="AB23" t="n">
         <v>296</v>
       </c>
-      <c r="AA23" t="n">
-        <v>236</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>286</v>
-      </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3770,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AL23" t="n">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="AM23" t="n">
         <v>450</v>
@@ -3847,22 +3835,22 @@
         <v>240</v>
       </c>
       <c r="O24" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="P24" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="Q24" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -3871,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -3880,25 +3868,25 @@
         <v>402</v>
       </c>
       <c r="Z24" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AA24" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AB24" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="AC24" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AD24" t="n">
         <v>1</v>
       </c>
       <c r="AE24" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -3907,7 +3895,7 @@
         <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="AJ24" t="n">
         <v>0</v>
@@ -3916,7 +3904,7 @@
         <v>402</v>
       </c>
       <c r="AL24" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AM24" t="n">
         <v>359</v>
@@ -3990,13 +3978,13 @@
         <v>285</v>
       </c>
       <c r="O25" t="n">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="P25" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -4020,19 +4008,19 @@
         <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="Z25" t="n">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="AA25" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="AB25" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -4056,10 +4044,10 @@
         <v>1</v>
       </c>
       <c r="AK25" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AL25" t="n">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="AM25" t="n">
         <v>308</v>
@@ -4133,25 +4121,25 @@
         <v>161</v>
       </c>
       <c r="O26" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="P26" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q26" t="n">
+        <v>18</v>
+      </c>
+      <c r="R26" t="n">
+        <v>20</v>
+      </c>
+      <c r="S26" t="n">
         <v>7</v>
       </c>
-      <c r="R26" t="n">
-        <v>19</v>
-      </c>
-      <c r="S26" t="n">
-        <v>11</v>
-      </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -4166,28 +4154,28 @@
         <v>472</v>
       </c>
       <c r="Z26" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AA26" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="AB26" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AC26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE26" t="n">
         <v>7</v>
       </c>
-      <c r="AD26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>11</v>
-      </c>
       <c r="AF26" t="n">
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH26" t="n">
         <v>0</v>
@@ -4202,7 +4190,7 @@
         <v>472</v>
       </c>
       <c r="AL26" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AM26" t="n">
         <v>419</v>
@@ -4276,13 +4264,13 @@
         <v>185</v>
       </c>
       <c r="O27" t="n">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="P27" t="n">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -4306,19 +4294,19 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="Z27" t="n">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="AA27" t="n">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="AB27" t="n">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="AC27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4342,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AL27" t="n">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="AM27" t="n">
         <v>342</v>
@@ -4419,19 +4407,19 @@
         <v>228</v>
       </c>
       <c r="O28" t="n">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="P28" t="n">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -4443,31 +4431,31 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="Z28" t="n">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="AA28" t="n">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="AB28" t="n">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="AC28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4479,16 +4467,16 @@
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AJ28" t="n">
         <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AL28" t="n">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="AM28" t="n">
         <v>384</v>
@@ -4562,13 +4550,13 @@
         <v>237</v>
       </c>
       <c r="O29" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="P29" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -4586,25 +4574,25 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="Z29" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="AA29" t="n">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="AB29" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="AC29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4622,16 +4610,16 @@
         <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AJ29" t="n">
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AL29" t="n">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="AM29" t="n">
         <v>357</v>
@@ -4705,22 +4693,22 @@
         <v>164</v>
       </c>
       <c r="O30" t="n">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="P30" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q30" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -4729,34 +4717,34 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="Z30" t="n">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="AA30" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB30" t="n">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -4771,10 +4759,10 @@
         <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="AL30" t="n">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="AM30" t="n">
         <v>457</v>
@@ -4851,13 +4839,13 @@
         <v>8</v>
       </c>
       <c r="P31" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="Q31" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -4881,19 +4869,19 @@
         <v>332</v>
       </c>
       <c r="Z31" t="n">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="AA31" t="n">
         <v>8</v>
       </c>
       <c r="AB31" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="AC31" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AD31" t="n">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4917,7 +4905,7 @@
         <v>332</v>
       </c>
       <c r="AL31" t="n">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="AM31" t="n">
         <v>315</v>
@@ -4991,19 +4979,19 @@
         <v>157</v>
       </c>
       <c r="O32" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P32" t="n">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="Q32" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -5015,31 +5003,31 @@
         <v>1</v>
       </c>
       <c r="W32" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="X32" t="n">
         <v>3</v>
       </c>
       <c r="Y32" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Z32" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AA32" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AB32" t="n">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="AC32" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -5051,16 +5039,16 @@
         <v>1</v>
       </c>
       <c r="AI32" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="AJ32" t="n">
         <v>3</v>
       </c>
       <c r="AK32" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL32" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AM32" t="n">
         <v>308</v>
@@ -5134,19 +5122,19 @@
         <v>164</v>
       </c>
       <c r="O33" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="P33" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
@@ -5158,31 +5146,31 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="Z33" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="AA33" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AB33" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="AC33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE33" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -5194,16 +5182,16 @@
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AJ33" t="n">
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AL33" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="AM33" t="n">
         <v>365</v>
@@ -5277,16 +5265,16 @@
         <v>80</v>
       </c>
       <c r="O34" t="n">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="P34" t="n">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -5301,28 +5289,28 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="Z34" t="n">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="AA34" t="n">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="AB34" t="n">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="AC34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -5337,16 +5325,16 @@
         <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AJ34" t="n">
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="AL34" t="n">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="AM34" t="n">
         <v>410</v>
@@ -5420,13 +5408,13 @@
         <v>89</v>
       </c>
       <c r="O35" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="P35" t="n">
         <v>182</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -5450,19 +5438,19 @@
         <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z35" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="AA35" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="AB35" t="n">
         <v>182</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5486,10 +5474,10 @@
         <v>1</v>
       </c>
       <c r="AK35" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AL35" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="AM35" t="n">
         <v>303</v>
@@ -5563,13 +5551,13 @@
         <v>115</v>
       </c>
       <c r="O36" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="P36" t="n">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="Q36" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -5593,19 +5581,19 @@
         <v>7</v>
       </c>
       <c r="Y36" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="Z36" t="n">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="AA36" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AB36" t="n">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="AC36" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5629,10 +5617,10 @@
         <v>7</v>
       </c>
       <c r="AK36" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AL36" t="n">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="AM36" t="n">
         <v>412</v>
@@ -5706,16 +5694,16 @@
         <v>171</v>
       </c>
       <c r="O37" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="P37" t="n">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -5730,28 +5718,28 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="Z37" t="n">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="AA37" t="n">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AB37" t="n">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="AC37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -5766,16 +5754,16 @@
         <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ37" t="n">
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="AL37" t="n">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="AM37" t="n">
         <v>371</v>
@@ -5849,19 +5837,19 @@
         <v>272</v>
       </c>
       <c r="O38" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="P38" t="n">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="Q38" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="R38" t="n">
         <v>2</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -5879,25 +5867,25 @@
         <v>4</v>
       </c>
       <c r="Y38" t="n">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="Z38" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AA38" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="AB38" t="n">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="AC38" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="AD38" t="n">
         <v>2</v>
       </c>
       <c r="AE38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -5915,10 +5903,10 @@
         <v>4</v>
       </c>
       <c r="AK38" t="n">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="AL38" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AM38" t="n">
         <v>453</v>
@@ -5992,22 +5980,22 @@
         <v>197</v>
       </c>
       <c r="O39" t="n">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="P39" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q39" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="R39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S39" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="T39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
         <v>1</v>
@@ -6025,25 +6013,25 @@
         <v>474</v>
       </c>
       <c r="Z39" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AA39" t="n">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AB39" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AC39" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="AD39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE39" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AF39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>1</v>
@@ -6061,7 +6049,7 @@
         <v>474</v>
       </c>
       <c r="AL39" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AM39" t="n">
         <v>445</v>
@@ -6135,19 +6123,19 @@
         <v>274</v>
       </c>
       <c r="O40" t="n">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="P40" t="n">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="Q40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -6165,25 +6153,25 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Z40" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AA40" t="n">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="AB40" t="n">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="AC40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -6201,10 +6189,10 @@
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL40" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AM40" t="n">
         <v>379</v>
@@ -6278,13 +6266,13 @@
         <v>235</v>
       </c>
       <c r="O41" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="P41" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="Q41" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -6308,19 +6296,19 @@
         <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Z41" t="n">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="AA41" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AB41" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="AC41" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -6344,10 +6332,10 @@
         <v>1</v>
       </c>
       <c r="AK41" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AL41" t="n">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="AM41" t="n">
         <v>335</v>
@@ -6421,16 +6409,16 @@
         <v>116</v>
       </c>
       <c r="O42" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="P42" t="n">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="Q42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -6445,28 +6433,28 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Z42" t="n">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="AA42" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="AB42" t="n">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="AC42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -6481,16 +6469,16 @@
         <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK42" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AL42" t="n">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="AM42" t="n">
         <v>371</v>
@@ -6564,19 +6552,19 @@
         <v>334</v>
       </c>
       <c r="O43" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="P43" t="n">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -6594,25 +6582,25 @@
         <v>1</v>
       </c>
       <c r="Y43" t="n">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="Z43" t="n">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="AA43" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="AB43" t="n">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="AC43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -6630,10 +6618,10 @@
         <v>1</v>
       </c>
       <c r="AK43" t="n">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="AL43" t="n">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="AM43" t="n">
         <v>331</v>
@@ -6707,19 +6695,19 @@
         <v>360</v>
       </c>
       <c r="O44" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="P44" t="n">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="Q44" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -6737,25 +6725,25 @@
         <v>3</v>
       </c>
       <c r="Y44" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="Z44" t="n">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="AA44" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="AB44" t="n">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="AC44" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -6773,10 +6761,10 @@
         <v>3</v>
       </c>
       <c r="AK44" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AL44" t="n">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="AM44" t="n">
         <v>301</v>
@@ -6850,16 +6838,16 @@
         <v>121</v>
       </c>
       <c r="O45" t="n">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="P45" t="n">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="R45" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="S45" t="n">
         <v>87</v>
@@ -6880,22 +6868,22 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="Z45" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="AA45" t="n">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="AB45" t="n">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="AC45" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AD45" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -6916,10 +6904,10 @@
         <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="AL45" t="n">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="AM45" t="n">
         <v>355</v>
@@ -6993,13 +6981,13 @@
         <v>144</v>
       </c>
       <c r="O46" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="P46" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q46" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="R46" t="n">
         <v>2</v>
@@ -7017,25 +7005,25 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X46" t="n">
         <v>6</v>
       </c>
       <c r="Y46" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Z46" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="AA46" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="AB46" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AC46" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="AD46" t="n">
         <v>2</v>
@@ -7053,16 +7041,16 @@
         <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AJ46" t="n">
         <v>6</v>
       </c>
       <c r="AK46" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AL46" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="AM46" t="n">
         <v>434</v>
@@ -7139,13 +7127,13 @@
         <v>170</v>
       </c>
       <c r="P47" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -7160,28 +7148,28 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="X47" t="n">
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="Z47" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AA47" t="n">
         <v>170</v>
       </c>
       <c r="AB47" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
@@ -7196,16 +7184,16 @@
         <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AJ47" t="n">
         <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="AL47" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AM47" t="n">
         <v>375</v>
@@ -7279,19 +7267,19 @@
         <v>136</v>
       </c>
       <c r="O48" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="P48" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="Q48" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T48" t="n">
         <v>0</v>
@@ -7303,31 +7291,31 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
+        <v>41</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>414</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>200</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>213</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>134</v>
+      </c>
+      <c r="AC48" t="n">
         <v>24</v>
       </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>413</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>192</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>220</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>145</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>22</v>
-      </c>
       <c r="AD48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
         <v>0</v>
@@ -7339,16 +7327,16 @@
         <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="AJ48" t="n">
         <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AL48" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="AM48" t="n">
         <v>363</v>
@@ -7425,7 +7413,7 @@
         <v>211</v>
       </c>
       <c r="P49" t="n">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -7434,7 +7422,7 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>
@@ -7446,7 +7434,7 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="X49" t="n">
         <v>0</v>
@@ -7461,10 +7449,10 @@
         <v>211</v>
       </c>
       <c r="AB49" t="n">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="AC49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -7482,7 +7470,7 @@
         <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AJ49" t="n">
         <v>0</v>
@@ -7565,19 +7553,19 @@
         <v>183</v>
       </c>
       <c r="O50" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P50" t="n">
         <v>192</v>
       </c>
       <c r="Q50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T50" t="n">
         <v>0</v>
@@ -7589,7 +7577,7 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="X50" t="n">
         <v>2</v>
@@ -7598,22 +7586,22 @@
         <v>450</v>
       </c>
       <c r="Z50" t="n">
+        <v>226</v>
+      </c>
+      <c r="AA50" t="n">
         <v>224</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>226</v>
       </c>
       <c r="AB50" t="n">
         <v>192</v>
       </c>
       <c r="AC50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF50" t="n">
         <v>0</v>
@@ -7625,7 +7613,7 @@
         <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AJ50" t="n">
         <v>2</v>
@@ -7634,7 +7622,7 @@
         <v>450</v>
       </c>
       <c r="AL50" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AM50" t="n">
         <v>372</v>
@@ -7708,19 +7696,19 @@
         <v>218</v>
       </c>
       <c r="O51" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="P51" t="n">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="Q51" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="R51" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T51" t="n">
         <v>0</v>
@@ -7732,31 +7720,31 @@
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="X51" t="n">
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="Z51" t="n">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="AA51" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="AB51" t="n">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="AC51" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="AD51" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AF51" t="n">
         <v>0</v>
@@ -7768,16 +7756,16 @@
         <v>0</v>
       </c>
       <c r="AI51" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="AJ51" t="n">
         <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AL51" t="n">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="AM51" t="n">
         <v>395</v>
@@ -7851,13 +7839,13 @@
         <v>224</v>
       </c>
       <c r="O52" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="P52" t="n">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="Q52" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -7875,25 +7863,25 @@
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X52" t="n">
         <v>1</v>
       </c>
       <c r="Y52" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="Z52" t="n">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="AA52" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="AB52" t="n">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="AC52" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AD52" t="n">
         <v>0</v>
@@ -7911,16 +7899,16 @@
         <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AJ52" t="n">
         <v>1</v>
       </c>
       <c r="AK52" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AL52" t="n">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="AM52" t="n">
         <v>378</v>
@@ -7994,16 +7982,16 @@
         <v>192</v>
       </c>
       <c r="O53" t="n">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="P53" t="n">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -8024,19 +8012,19 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z53" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="AA53" t="n">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="AB53" t="n">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="AC53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD53" t="n">
         <v>5</v>
@@ -8060,10 +8048,10 @@
         <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AL53" t="n">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="AM53" t="n">
         <v>429</v>
@@ -8137,16 +8125,16 @@
         <v>91</v>
       </c>
       <c r="O54" t="n">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="P54" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R54" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S54" t="n">
         <v>22</v>
@@ -8170,19 +8158,19 @@
         <v>424</v>
       </c>
       <c r="Z54" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="AA54" t="n">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="AB54" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AC54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD54" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE54" t="n">
         <v>22</v>
@@ -8206,7 +8194,7 @@
         <v>424</v>
       </c>
       <c r="AL54" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="AM54" t="n">
         <v>396</v>
@@ -8280,25 +8268,25 @@
         <v>212</v>
       </c>
       <c r="O55" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P55" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Q55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -8313,28 +8301,28 @@
         <v>374</v>
       </c>
       <c r="Z55" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AA55" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AB55" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="AC55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
         <v>1</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH55" t="n">
         <v>0</v>
@@ -8349,7 +8337,7 @@
         <v>374</v>
       </c>
       <c r="AL55" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM55" t="n">
         <v>279</v>
@@ -8423,19 +8411,19 @@
         <v>72</v>
       </c>
       <c r="O56" t="n">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="P56" t="n">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T56" t="n">
         <v>0</v>
@@ -8447,31 +8435,31 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="X56" t="n">
         <v>1</v>
       </c>
       <c r="Y56" t="n">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="Z56" t="n">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="AA56" t="n">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="AB56" t="n">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AE56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF56" t="n">
         <v>0</v>
@@ -8483,16 +8471,16 @@
         <v>0</v>
       </c>
       <c r="AI56" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AJ56" t="n">
         <v>1</v>
       </c>
       <c r="AK56" t="n">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="AL56" t="n">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="AM56" t="n">
         <v>420</v>
@@ -8566,16 +8554,16 @@
         <v>262</v>
       </c>
       <c r="O57" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="P57" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="Q57" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -8590,28 +8578,28 @@
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="X57" t="n">
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="Z57" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="AA57" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="AB57" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="AC57" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AD57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -8626,16 +8614,16 @@
         <v>0</v>
       </c>
       <c r="AI57" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ57" t="n">
         <v>0</v>
       </c>
       <c r="AK57" t="n">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AL57" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="AM57" t="n">
         <v>336</v>
@@ -8709,22 +8697,22 @@
         <v>81</v>
       </c>
       <c r="O58" t="n">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="P58" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="Q58" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -8733,34 +8721,34 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="X58" t="n">
         <v>2</v>
       </c>
       <c r="Y58" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="Z58" t="n">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA58" t="n">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="AB58" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AC58" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AD58" t="n">
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -8769,16 +8757,16 @@
         <v>0</v>
       </c>
       <c r="AI58" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AJ58" t="n">
         <v>2</v>
       </c>
       <c r="AK58" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AL58" t="n">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AM58" t="n">
         <v>363</v>
@@ -8852,16 +8840,16 @@
         <v>174</v>
       </c>
       <c r="O59" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="P59" t="n">
         <v>153</v>
       </c>
       <c r="Q59" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="R59" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -8882,22 +8870,22 @@
         <v>4</v>
       </c>
       <c r="Y59" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Z59" t="n">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="AA59" t="n">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="AB59" t="n">
         <v>153</v>
       </c>
       <c r="AC59" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="AD59" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -8918,10 +8906,10 @@
         <v>4</v>
       </c>
       <c r="AK59" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AL59" t="n">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="AM59" t="n">
         <v>383</v>
@@ -8995,76 +8983,76 @@
         <v>144</v>
       </c>
       <c r="O60" t="n">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P60" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Q60" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="R60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S60" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="T60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="X60" t="n">
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z60" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="AA60" t="n">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="AB60" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AC60" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AD60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE60" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AF60" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="n">
         <v>0</v>
       </c>
       <c r="AI60" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AJ60" t="n">
         <v>0</v>
       </c>
       <c r="AK60" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL60" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="AM60" t="n">
         <v>377</v>
@@ -9281,22 +9269,22 @@
         <v>168</v>
       </c>
       <c r="O62" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="P62" t="n">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="Q62" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>1</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -9311,28 +9299,28 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="Z62" t="n">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="AA62" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="AB62" t="n">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="AC62" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
         <v>1</v>
       </c>
       <c r="AE62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -9347,10 +9335,10 @@
         <v>0</v>
       </c>
       <c r="AK62" t="n">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="AL62" t="n">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="AM62" t="n">
         <v>365</v>
@@ -9424,13 +9412,13 @@
         <v>135</v>
       </c>
       <c r="O63" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="P63" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="Q63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -9454,19 +9442,19 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="Z63" t="n">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="AA63" t="n">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="AB63" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="AC63" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -9490,10 +9478,10 @@
         <v>0</v>
       </c>
       <c r="AK63" t="n">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AL63" t="n">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="AM63" t="n">
         <v>324</v>
@@ -9567,19 +9555,19 @@
         <v>196</v>
       </c>
       <c r="O64" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="P64" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64" t="n">
         <v>0</v>
@@ -9597,16 +9585,16 @@
         <v>2</v>
       </c>
       <c r="Y64" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="Z64" t="n">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="AA64" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="AB64" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -9615,7 +9603,7 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF64" t="n">
         <v>0</v>
@@ -9633,10 +9621,10 @@
         <v>2</v>
       </c>
       <c r="AK64" t="n">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AL64" t="n">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="AM64" t="n">
         <v>440</v>
@@ -9710,19 +9698,19 @@
         <v>233</v>
       </c>
       <c r="O65" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P65" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="Q65" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T65" t="n">
         <v>0</v>
@@ -9740,25 +9728,25 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Z65" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AA65" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AB65" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="AC65" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF65" t="n">
         <v>0</v>
@@ -9776,10 +9764,10 @@
         <v>0</v>
       </c>
       <c r="AK65" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AL65" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AM65" t="n">
         <v>417</v>
@@ -9853,19 +9841,19 @@
         <v>150</v>
       </c>
       <c r="O66" t="n">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="P66" t="n">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T66" t="n">
         <v>0</v>
@@ -9880,28 +9868,28 @@
         <v>21</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y66" t="n">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="Z66" t="n">
-        <v>240</v>
+        <v>282</v>
       </c>
       <c r="AA66" t="n">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="AB66" t="n">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="AC66" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF66" t="n">
         <v>0</v>
@@ -9919,10 +9907,10 @@
         <v>1</v>
       </c>
       <c r="AK66" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL66" t="n">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="AM66" t="n">
         <v>384</v>
@@ -9996,19 +9984,19 @@
         <v>99</v>
       </c>
       <c r="O67" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="P67" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="Q67" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T67" t="n">
         <v>0</v>
@@ -10026,25 +10014,25 @@
         <v>5</v>
       </c>
       <c r="Y67" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="Z67" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="AA67" t="n">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="AB67" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="AC67" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AF67" t="n">
         <v>0</v>
@@ -10062,10 +10050,10 @@
         <v>5</v>
       </c>
       <c r="AK67" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AL67" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="AM67" t="n">
         <v>297</v>
@@ -10139,19 +10127,19 @@
         <v>163</v>
       </c>
       <c r="O68" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="P68" t="n">
-        <v>363</v>
+        <v>414</v>
       </c>
       <c r="Q68" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="R68" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68" t="n">
         <v>0</v>
@@ -10163,31 +10151,31 @@
         <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="X68" t="n">
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="Z68" t="n">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="AA68" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="AB68" t="n">
-        <v>363</v>
+        <v>414</v>
       </c>
       <c r="AC68" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="AD68" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF68" t="n">
         <v>0</v>
@@ -10199,16 +10187,16 @@
         <v>0</v>
       </c>
       <c r="AI68" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AJ68" t="n">
         <v>0</v>
       </c>
       <c r="AK68" t="n">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="AL68" t="n">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="AM68" t="n">
         <v>395</v>
@@ -10282,19 +10270,19 @@
         <v>124</v>
       </c>
       <c r="O69" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="P69" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Q69" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="R69" t="n">
         <v>1</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T69" t="n">
         <v>0</v>
@@ -10306,31 +10294,31 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X69" t="n">
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Z69" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AA69" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AB69" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AC69" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="AD69" t="n">
         <v>1</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF69" t="n">
         <v>0</v>
@@ -10342,16 +10330,16 @@
         <v>0</v>
       </c>
       <c r="AI69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ69" t="n">
         <v>0</v>
       </c>
       <c r="AK69" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AL69" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AM69" t="n">
         <v>317</v>
@@ -10425,19 +10413,19 @@
         <v>77</v>
       </c>
       <c r="O70" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="P70" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70" t="n">
         <v>0</v>
@@ -10458,22 +10446,22 @@
         <v>346</v>
       </c>
       <c r="Z70" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AA70" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AB70" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF70" t="n">
         <v>0</v>
@@ -10494,7 +10482,7 @@
         <v>346</v>
       </c>
       <c r="AL70" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AM70" t="n">
         <v>306</v>
@@ -10568,16 +10556,16 @@
         <v>202</v>
       </c>
       <c r="O71" t="n">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="P71" t="n">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="Q71" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R71" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -10598,22 +10586,22 @@
         <v>1</v>
       </c>
       <c r="Y71" t="n">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="Z71" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="AA71" t="n">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="AB71" t="n">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="AC71" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AD71" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="AE71" t="n">
         <v>0</v>
@@ -10634,10 +10622,10 @@
         <v>1</v>
       </c>
       <c r="AK71" t="n">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="AL71" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="AM71" t="n">
         <v>366</v>
@@ -10711,16 +10699,16 @@
         <v>249</v>
       </c>
       <c r="O72" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="P72" t="n">
-        <v>411</v>
+        <v>451</v>
       </c>
       <c r="Q72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -10741,22 +10729,22 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="Z72" t="n">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="AA72" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="AB72" t="n">
-        <v>411</v>
+        <v>451</v>
       </c>
       <c r="AC72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE72" t="n">
         <v>0</v>
@@ -10777,10 +10765,10 @@
         <v>0</v>
       </c>
       <c r="AK72" t="n">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="AL72" t="n">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="AM72" t="n">
         <v>353</v>
@@ -10854,10 +10842,10 @@
         <v>57</v>
       </c>
       <c r="O73" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="P73" t="n">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -10878,22 +10866,22 @@
         <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="X73" t="n">
         <v>1</v>
       </c>
       <c r="Y73" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Z73" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AA73" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AB73" t="n">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -10914,16 +10902,16 @@
         <v>0</v>
       </c>
       <c r="AI73" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AJ73" t="n">
         <v>1</v>
       </c>
       <c r="AK73" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AL73" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AM73" t="n">
         <v>362</v>
@@ -10997,16 +10985,16 @@
         <v>405</v>
       </c>
       <c r="O74" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P74" t="n">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -11021,28 +11009,28 @@
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="X74" t="n">
         <v>1</v>
       </c>
       <c r="Y74" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Z74" t="n">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="AA74" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB74" t="n">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="AC74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="AE74" t="n">
         <v>0</v>
@@ -11057,16 +11045,16 @@
         <v>0</v>
       </c>
       <c r="AI74" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AJ74" t="n">
         <v>1</v>
       </c>
       <c r="AK74" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AL74" t="n">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="AM74" t="n">
         <v>398</v>
@@ -11140,55 +11128,55 @@
         <v>121</v>
       </c>
       <c r="O75" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="P75" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="Q75" t="n">
+        <v>5</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="n">
+        <v>31</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>413</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>251</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>161</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>214</v>
+      </c>
+      <c r="AC75" t="n">
         <v>4</v>
       </c>
-      <c r="R75" t="n">
-        <v>3</v>
-      </c>
-      <c r="S75" t="n">
-        <v>9</v>
-      </c>
-      <c r="T75" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" t="n">
-        <v>0</v>
-      </c>
-      <c r="V75" t="n">
-        <v>0</v>
-      </c>
-      <c r="W75" t="n">
-        <v>30</v>
-      </c>
-      <c r="X75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>411</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>245</v>
-      </c>
-      <c r="AA75" t="n">
-        <v>164</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>202</v>
-      </c>
-      <c r="AC75" t="n">
-        <v>3</v>
-      </c>
       <c r="AD75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE75" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AF75" t="n">
         <v>0</v>
@@ -11200,16 +11188,16 @@
         <v>0</v>
       </c>
       <c r="AI75" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AJ75" t="n">
         <v>0</v>
       </c>
       <c r="AK75" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AL75" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="AM75" t="n">
         <v>359</v>
@@ -11283,13 +11271,13 @@
         <v>90</v>
       </c>
       <c r="O76" t="n">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="P76" t="n">
         <v>133</v>
       </c>
       <c r="Q76" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
@@ -11313,19 +11301,19 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="Z76" t="n">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="AA76" t="n">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="AB76" t="n">
         <v>133</v>
       </c>
       <c r="AC76" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -11349,10 +11337,10 @@
         <v>0</v>
       </c>
       <c r="AK76" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AL76" t="n">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="AM76" t="n">
         <v>357</v>
@@ -11426,19 +11414,19 @@
         <v>122</v>
       </c>
       <c r="O77" t="n">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="P77" t="n">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="Q77" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T77" t="n">
         <v>0</v>
@@ -11450,31 +11438,31 @@
         <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="X77" t="n">
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="Z77" t="n">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="AA77" t="n">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="AB77" t="n">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="AC77" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
         <v>9</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF77" t="n">
         <v>0</v>
@@ -11486,16 +11474,16 @@
         <v>0</v>
       </c>
       <c r="AI77" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="AJ77" t="n">
         <v>0</v>
       </c>
       <c r="AK77" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AL77" t="n">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="AM77" t="n">
         <v>386</v>
@@ -11569,19 +11557,19 @@
         <v>120</v>
       </c>
       <c r="O78" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="P78" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q78" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T78" t="n">
         <v>0</v>
@@ -11593,31 +11581,31 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X78" t="n">
         <v>1</v>
       </c>
       <c r="Y78" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="Z78" t="n">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="AA78" t="n">
         <v>150</v>
       </c>
       <c r="AB78" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AC78" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF78" t="n">
         <v>0</v>
@@ -11629,16 +11617,16 @@
         <v>0</v>
       </c>
       <c r="AI78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ78" t="n">
         <v>1</v>
       </c>
       <c r="AK78" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AL78" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AM78" t="n">
         <v>350</v>
@@ -11712,13 +11700,13 @@
         <v>260</v>
       </c>
       <c r="O79" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="P79" t="n">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="Q79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
@@ -11742,19 +11730,19 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Z79" t="n">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="AA79" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AB79" t="n">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="AC79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -11778,10 +11766,10 @@
         <v>0</v>
       </c>
       <c r="AK79" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AL79" t="n">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="AM79" t="n">
         <v>319</v>
@@ -11858,7 +11846,7 @@
         <v>96</v>
       </c>
       <c r="P80" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -11867,7 +11855,7 @@
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T80" t="n">
         <v>0</v>
@@ -11894,7 +11882,7 @@
         <v>96</v>
       </c>
       <c r="AB80" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -11903,7 +11891,7 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF80" t="n">
         <v>0</v>
@@ -12141,19 +12129,19 @@
         <v>274</v>
       </c>
       <c r="O82" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="P82" t="n">
         <v>218</v>
       </c>
       <c r="Q82" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T82" t="n">
         <v>0</v>
@@ -12171,25 +12159,25 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="Z82" t="n">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="AA82" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="AB82" t="n">
         <v>218</v>
       </c>
       <c r="AC82" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF82" t="n">
         <v>0</v>
@@ -12207,10 +12195,10 @@
         <v>0</v>
       </c>
       <c r="AK82" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AL82" t="n">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="AM82" t="n">
         <v>385</v>
@@ -12284,19 +12272,19 @@
         <v>140</v>
       </c>
       <c r="O83" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="P83" t="n">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="Q83" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T83" t="n">
         <v>0</v>
@@ -12314,25 +12302,25 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Z83" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AA83" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AB83" t="n">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="AC83" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AF83" t="n">
         <v>0</v>
@@ -12350,10 +12338,10 @@
         <v>0</v>
       </c>
       <c r="AK83" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AL83" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AM83" t="n">
         <v>340</v>
@@ -12427,16 +12415,16 @@
         <v>45</v>
       </c>
       <c r="O84" t="n">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="P84" t="n">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="Q84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -12451,28 +12439,28 @@
         <v>0</v>
       </c>
       <c r="W84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X84" t="n">
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Z84" t="n">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="AA84" t="n">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="AB84" t="n">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
       </c>
       <c r="AD84" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AE84" t="n">
         <v>0</v>
@@ -12487,16 +12475,16 @@
         <v>0</v>
       </c>
       <c r="AI84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AJ84" t="n">
         <v>0</v>
       </c>
       <c r="AK84" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AL84" t="n">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="AM84" t="n">
         <v>378</v>
@@ -12570,13 +12558,13 @@
         <v>264</v>
       </c>
       <c r="O85" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="P85" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="Q85" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R85" t="n">
         <v>0</v>
@@ -12594,25 +12582,25 @@
         <v>0</v>
       </c>
       <c r="W85" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="X85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="Z85" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AA85" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="AB85" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="AC85" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -12630,16 +12618,16 @@
         <v>0</v>
       </c>
       <c r="AI85" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AJ85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK85" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AL85" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AM85" t="n">
         <v>367</v>
@@ -12713,22 +12701,22 @@
         <v>175</v>
       </c>
       <c r="O86" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P86" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="Q86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R86" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S86" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="T86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -12737,7 +12725,7 @@
         <v>0</v>
       </c>
       <c r="W86" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="X86" t="n">
         <v>0</v>
@@ -12746,25 +12734,25 @@
         <v>447</v>
       </c>
       <c r="Z86" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AA86" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AB86" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="AC86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE86" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AF86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -12773,7 +12761,7 @@
         <v>0</v>
       </c>
       <c r="AI86" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AJ86" t="n">
         <v>0</v>
@@ -12782,7 +12770,7 @@
         <v>447</v>
       </c>
       <c r="AL86" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AM86" t="n">
         <v>367</v>
@@ -12856,16 +12844,16 @@
         <v>145</v>
       </c>
       <c r="O87" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="P87" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R87" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="S87" t="n">
         <v>27</v>
@@ -12880,28 +12868,28 @@
         <v>0</v>
       </c>
       <c r="W87" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="X87" t="n">
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Z87" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AA87" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="AB87" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AC87" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AD87" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AE87" t="n">
         <v>27</v>
@@ -12916,16 +12904,16 @@
         <v>0</v>
       </c>
       <c r="AI87" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AJ87" t="n">
         <v>0</v>
       </c>
       <c r="AK87" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AL87" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AM87" t="n">
         <v>360</v>
@@ -12999,16 +12987,16 @@
         <v>137</v>
       </c>
       <c r="O88" t="n">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="P88" t="n">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="Q88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R88" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="S88" t="n">
         <v>1</v>
@@ -13023,28 +13011,28 @@
         <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="X88" t="n">
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="Z88" t="n">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="AA88" t="n">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="AB88" t="n">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD88" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -13059,16 +13047,16 @@
         <v>0</v>
       </c>
       <c r="AI88" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AJ88" t="n">
         <v>0</v>
       </c>
       <c r="AK88" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AL88" t="n">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="AM88" t="n">
         <v>356</v>
@@ -13142,19 +13130,19 @@
         <v>86</v>
       </c>
       <c r="O89" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="P89" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q89" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="R89" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T89" t="n">
         <v>0</v>
@@ -13166,7 +13154,7 @@
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="X89" t="n">
         <v>0</v>
@@ -13175,22 +13163,22 @@
         <v>492</v>
       </c>
       <c r="Z89" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AA89" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AB89" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AC89" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="AD89" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF89" t="n">
         <v>0</v>
@@ -13202,7 +13190,7 @@
         <v>0</v>
       </c>
       <c r="AI89" t="n">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="AJ89" t="n">
         <v>0</v>
@@ -13211,7 +13199,7 @@
         <v>492</v>
       </c>
       <c r="AL89" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AM89" t="n">
         <v>405</v>
@@ -13285,16 +13273,16 @@
         <v>98</v>
       </c>
       <c r="O90" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="P90" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -13309,28 +13297,28 @@
         <v>0</v>
       </c>
       <c r="W90" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y90" t="n">
         <v>323</v>
       </c>
       <c r="Z90" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AA90" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="AB90" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
       </c>
       <c r="AD90" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="AE90" t="n">
         <v>0</v>
@@ -13345,16 +13333,16 @@
         <v>0</v>
       </c>
       <c r="AI90" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK90" t="n">
         <v>323</v>
       </c>
       <c r="AL90" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AM90" t="n">
         <v>301</v>
@@ -13428,13 +13416,13 @@
         <v>66</v>
       </c>
       <c r="O91" t="n">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="P91" t="n">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="Q91" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R91" t="n">
         <v>0</v>
@@ -13458,19 +13446,19 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="Z91" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="AA91" t="n">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="AB91" t="n">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="AC91" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AD91" t="n">
         <v>0</v>
@@ -13494,10 +13482,10 @@
         <v>0</v>
       </c>
       <c r="AK91" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="AL91" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="AM91" t="n">
         <v>399</v>
@@ -13571,13 +13559,13 @@
         <v>167</v>
       </c>
       <c r="O92" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="P92" t="n">
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="Q92" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
         <v>5</v>
@@ -13601,19 +13589,19 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="Z92" t="n">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="AA92" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AB92" t="n">
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="AC92" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="AD92" t="n">
         <v>5</v>
@@ -13637,10 +13625,10 @@
         <v>0</v>
       </c>
       <c r="AK92" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AL92" t="n">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="AM92" t="n">
         <v>364</v>
@@ -13714,10 +13702,10 @@
         <v>103</v>
       </c>
       <c r="O93" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="P93" t="n">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -13726,7 +13714,7 @@
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
         <v>0</v>
@@ -13744,16 +13732,16 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="Z93" t="n">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="AA93" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="AB93" t="n">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -13762,7 +13750,7 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
         <v>0</v>
@@ -13780,10 +13768,10 @@
         <v>0</v>
       </c>
       <c r="AK93" t="n">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AL93" t="n">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="AM93" t="n">
         <v>335</v>
@@ -13860,16 +13848,16 @@
         <v>198</v>
       </c>
       <c r="P94" t="n">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="Q94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T94" t="n">
         <v>0</v>
@@ -13881,7 +13869,7 @@
         <v>1</v>
       </c>
       <c r="W94" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="X94" t="n">
         <v>0</v>
@@ -13890,22 +13878,22 @@
         <v>408</v>
       </c>
       <c r="Z94" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AA94" t="n">
         <v>198</v>
       </c>
       <c r="AB94" t="n">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="AC94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
         <v>0</v>
@@ -13917,7 +13905,7 @@
         <v>1</v>
       </c>
       <c r="AI94" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="AJ94" t="n">
         <v>0</v>
@@ -13926,7 +13914,7 @@
         <v>408</v>
       </c>
       <c r="AL94" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM94" t="n">
         <v>373</v>
@@ -14000,19 +13988,19 @@
         <v>135</v>
       </c>
       <c r="O95" t="n">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="P95" t="n">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="Q95" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T95" t="n">
         <v>0</v>
@@ -14030,25 +14018,25 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="Z95" t="n">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="AA95" t="n">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="AB95" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="AC95" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF95" t="n">
         <v>0</v>
@@ -14066,10 +14054,10 @@
         <v>0</v>
       </c>
       <c r="AK95" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AL95" t="n">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="AM95" t="n">
         <v>356</v>
@@ -14143,19 +14131,19 @@
         <v>147</v>
       </c>
       <c r="O96" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="P96" t="n">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="Q96" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T96" t="n">
         <v>0</v>
@@ -14173,25 +14161,25 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="Z96" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="AA96" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="AB96" t="n">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="AC96" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="AD96" t="n">
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF96" t="n">
         <v>0</v>
@@ -14209,10 +14197,10 @@
         <v>0</v>
       </c>
       <c r="AK96" t="n">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="AL96" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="AM96" t="n">
         <v>282</v>
@@ -14286,49 +14274,49 @@
         <v>168</v>
       </c>
       <c r="O97" t="n">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="P97" t="n">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="Q97" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="R97" t="n">
         <v>44</v>
       </c>
       <c r="S97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T97" t="n">
         <v>0</v>
       </c>
       <c r="U97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V97" t="n">
         <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y97" t="n">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="Z97" t="n">
-        <v>207</v>
+        <v>240</v>
       </c>
       <c r="AA97" t="n">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="AB97" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="AC97" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="AD97" t="n">
         <v>44</v>
@@ -14340,22 +14328,22 @@
         <v>0</v>
       </c>
       <c r="AG97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH97" t="n">
         <v>0</v>
       </c>
       <c r="AI97" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AJ97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK97" t="n">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AL97" t="n">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="AM97" t="n">
         <v>378</v>
@@ -14429,19 +14417,19 @@
         <v>65</v>
       </c>
       <c r="O98" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P98" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="Q98" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R98" t="n">
         <v>9</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T98" t="n">
         <v>0</v>
@@ -14462,22 +14450,22 @@
         <v>399</v>
       </c>
       <c r="Z98" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA98" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AB98" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="AC98" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AD98" t="n">
         <v>9</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF98" t="n">
         <v>0</v>
@@ -14498,7 +14486,7 @@
         <v>399</v>
       </c>
       <c r="AL98" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM98" t="n">
         <v>367</v>
@@ -14572,10 +14560,10 @@
         <v>238</v>
       </c>
       <c r="O99" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="P99" t="n">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -14584,7 +14572,7 @@
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T99" t="n">
         <v>0</v>
@@ -14602,16 +14590,16 @@
         <v>2</v>
       </c>
       <c r="Y99" t="n">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="Z99" t="n">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="AA99" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="AB99" t="n">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -14620,7 +14608,7 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF99" t="n">
         <v>0</v>
@@ -14638,10 +14626,10 @@
         <v>2</v>
       </c>
       <c r="AK99" t="n">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="AL99" t="n">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="AM99" t="n">
         <v>321</v>
@@ -14715,19 +14703,19 @@
         <v>152</v>
       </c>
       <c r="O100" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="P100" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="Q100" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T100" t="n">
         <v>0</v>
@@ -14739,31 +14727,31 @@
         <v>0</v>
       </c>
       <c r="W100" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="X100" t="n">
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="Z100" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="AA100" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="AB100" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="AC100" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF100" t="n">
         <v>0</v>
@@ -14775,16 +14763,16 @@
         <v>0</v>
       </c>
       <c r="AI100" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AJ100" t="n">
         <v>0</v>
       </c>
       <c r="AK100" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AL100" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="AM100" t="n">
         <v>343</v>
@@ -14858,58 +14846,58 @@
         <v>206</v>
       </c>
       <c r="O101" t="n">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="P101" t="n">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="n">
+        <v>1</v>
+      </c>
+      <c r="V101" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" t="n">
+        <v>84</v>
+      </c>
+      <c r="X101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>509</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>311</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>199</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>219</v>
+      </c>
+      <c r="AC101" t="n">
         <v>2</v>
       </c>
-      <c r="U101" t="n">
-        <v>1</v>
-      </c>
-      <c r="V101" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" t="n">
-        <v>82</v>
-      </c>
-      <c r="X101" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y101" t="n">
-        <v>502</v>
-      </c>
-      <c r="Z101" t="n">
-        <v>290</v>
-      </c>
-      <c r="AA101" t="n">
-        <v>212</v>
-      </c>
-      <c r="AB101" t="n">
-        <v>203</v>
-      </c>
-      <c r="AC101" t="n">
-        <v>0</v>
-      </c>
       <c r="AD101" t="n">
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>1</v>
@@ -14918,16 +14906,16 @@
         <v>0</v>
       </c>
       <c r="AI101" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AJ101" t="n">
         <v>1</v>
       </c>
       <c r="AK101" t="n">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="AL101" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="AM101" t="n">
         <v>455</v>
@@ -15001,13 +14989,13 @@
         <v>212</v>
       </c>
       <c r="O102" t="n">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="P102" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="Q102" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="R102" t="n">
         <v>5</v>
@@ -15031,19 +15019,19 @@
         <v>2</v>
       </c>
       <c r="Y102" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Z102" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="AA102" t="n">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="AB102" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="AC102" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AD102" t="n">
         <v>5</v>
@@ -15067,10 +15055,10 @@
         <v>2</v>
       </c>
       <c r="AK102" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AL102" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="AM102" t="n">
         <v>472</v>
@@ -15144,10 +15132,10 @@
         <v>117</v>
       </c>
       <c r="O103" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="P103" t="n">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
@@ -15156,7 +15144,7 @@
         <v>1</v>
       </c>
       <c r="S103" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T103" t="n">
         <v>0</v>
@@ -15174,25 +15162,25 @@
         <v>1</v>
       </c>
       <c r="Y103" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="Z103" t="n">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="AA103" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="AB103" t="n">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD103" t="n">
         <v>1</v>
       </c>
       <c r="AE103" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
         <v>0</v>
@@ -15210,10 +15198,10 @@
         <v>1</v>
       </c>
       <c r="AK103" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AL103" t="n">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="AM103" t="n">
         <v>316</v>
@@ -15287,19 +15275,19 @@
         <v>220</v>
       </c>
       <c r="O104" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P104" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q104" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="R104" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="S104" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T104" t="n">
         <v>0</v>
@@ -15317,25 +15305,25 @@
         <v>3</v>
       </c>
       <c r="Y104" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="Z104" t="n">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="AA104" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AB104" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AC104" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="AD104" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AE104" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AF104" t="n">
         <v>0</v>
@@ -15353,10 +15341,10 @@
         <v>3</v>
       </c>
       <c r="AK104" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AL104" t="n">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="AM104" t="n">
         <v>422</v>
@@ -15430,16 +15418,16 @@
         <v>191</v>
       </c>
       <c r="O105" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="P105" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="Q105" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="R105" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -15460,22 +15448,22 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="Z105" t="n">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="AA105" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="AB105" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="AC105" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="AD105" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE105" t="n">
         <v>0</v>
@@ -15496,10 +15484,10 @@
         <v>0</v>
       </c>
       <c r="AK105" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AL105" t="n">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="AM105" t="n">
         <v>391</v>
@@ -15573,10 +15561,10 @@
         <v>200</v>
       </c>
       <c r="O106" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="P106" t="n">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -15585,7 +15573,7 @@
         <v>1</v>
       </c>
       <c r="S106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T106" t="n">
         <v>0</v>
@@ -15597,22 +15585,22 @@
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="X106" t="n">
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="Z106" t="n">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="AA106" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="AB106" t="n">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -15621,7 +15609,7 @@
         <v>1</v>
       </c>
       <c r="AE106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF106" t="n">
         <v>0</v>
@@ -15633,16 +15621,16 @@
         <v>0</v>
       </c>
       <c r="AI106" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AJ106" t="n">
         <v>0</v>
       </c>
       <c r="AK106" t="n">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="AL106" t="n">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="AM106" t="n">
         <v>366</v>
@@ -15716,13 +15704,13 @@
         <v>251</v>
       </c>
       <c r="O107" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="P107" t="n">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="Q107" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
@@ -15749,16 +15737,16 @@
         <v>367</v>
       </c>
       <c r="Z107" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="AA107" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="AB107" t="n">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="AC107" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AD107" t="n">
         <v>0</v>
@@ -15785,7 +15773,7 @@
         <v>367</v>
       </c>
       <c r="AL107" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="AM107" t="n">
         <v>322</v>
@@ -15859,19 +15847,19 @@
         <v>228</v>
       </c>
       <c r="O108" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="P108" t="n">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="Q108" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T108" t="n">
         <v>0</v>
@@ -15892,22 +15880,22 @@
         <v>382</v>
       </c>
       <c r="Z108" t="n">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="AA108" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="AB108" t="n">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="AC108" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AD108" t="n">
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF108" t="n">
         <v>0</v>
@@ -15928,7 +15916,7 @@
         <v>382</v>
       </c>
       <c r="AL108" t="n">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="AM108" t="n">
         <v>324</v>
@@ -16002,19 +15990,19 @@
         <v>47</v>
       </c>
       <c r="O109" t="n">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="P109" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="Q109" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
       <c r="S109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T109" t="n">
         <v>0</v>
@@ -16026,31 +16014,31 @@
         <v>0</v>
       </c>
       <c r="W109" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="X109" t="n">
         <v>1</v>
       </c>
       <c r="Y109" t="n">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="Z109" t="n">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="AA109" t="n">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="AB109" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AC109" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AD109" t="n">
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
         <v>0</v>
@@ -16062,16 +16050,16 @@
         <v>0</v>
       </c>
       <c r="AI109" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="AJ109" t="n">
         <v>1</v>
       </c>
       <c r="AK109" t="n">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="AL109" t="n">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="AM109" t="n">
         <v>407</v>
@@ -16145,19 +16133,19 @@
         <v>324</v>
       </c>
       <c r="O110" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="P110" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="Q110" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
         <v>5</v>
       </c>
       <c r="S110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T110" t="n">
         <v>0</v>
@@ -16172,28 +16160,28 @@
         <v>20</v>
       </c>
       <c r="X110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y110" t="n">
         <v>622</v>
       </c>
       <c r="Z110" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AA110" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="AB110" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="AC110" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AD110" t="n">
         <v>5</v>
       </c>
       <c r="AE110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF110" t="n">
         <v>0</v>
@@ -16208,13 +16196,13 @@
         <v>20</v>
       </c>
       <c r="AJ110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK110" t="n">
         <v>622</v>
       </c>
       <c r="AL110" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AM110" t="n">
         <v>507</v>
@@ -16288,13 +16276,13 @@
         <v>68</v>
       </c>
       <c r="O111" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="P111" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="Q111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R111" t="n">
         <v>2</v>
@@ -16318,19 +16306,19 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="Z111" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="AA111" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AB111" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="AC111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD111" t="n">
         <v>2</v>
@@ -16354,10 +16342,10 @@
         <v>0</v>
       </c>
       <c r="AK111" t="n">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AL111" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="AM111" t="n">
         <v>294</v>
@@ -16431,10 +16419,10 @@
         <v>34</v>
       </c>
       <c r="O112" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="P112" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
@@ -16455,22 +16443,22 @@
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="X112" t="n">
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="Z112" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="AA112" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="AB112" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -16491,16 +16479,16 @@
         <v>0</v>
       </c>
       <c r="AI112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AJ112" t="n">
         <v>0</v>
       </c>
       <c r="AK112" t="n">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="AL112" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="AM112" t="n">
         <v>403</v>
@@ -16574,19 +16562,19 @@
         <v>163</v>
       </c>
       <c r="O113" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="P113" t="n">
-        <v>194</v>
+        <v>278</v>
       </c>
       <c r="Q113" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T113" t="n">
         <v>0</v>
@@ -16598,31 +16586,31 @@
         <v>0</v>
       </c>
       <c r="W113" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="X113" t="n">
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="Z113" t="n">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="AA113" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="AB113" t="n">
-        <v>194</v>
+        <v>278</v>
       </c>
       <c r="AC113" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="AD113" t="n">
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AF113" t="n">
         <v>0</v>
@@ -16634,16 +16622,16 @@
         <v>0</v>
       </c>
       <c r="AI113" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AJ113" t="n">
         <v>0</v>
       </c>
       <c r="AK113" t="n">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="AL113" t="n">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="AM113" t="n">
         <v>362</v>
@@ -16720,10 +16708,10 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="Q114" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
@@ -16741,7 +16729,7 @@
         <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="X114" t="n">
         <v>4</v>
@@ -16756,10 +16744,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="AC114" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -16777,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="AI114" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AJ114" t="n">
         <v>4</v>
@@ -16863,7 +16851,7 @@
         <v>212</v>
       </c>
       <c r="P115" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Q115" t="n">
         <v>6</v>
@@ -16884,7 +16872,7 @@
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X115" t="n">
         <v>0</v>
@@ -16899,7 +16887,7 @@
         <v>212</v>
       </c>
       <c r="AB115" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AC115" t="n">
         <v>6</v>
@@ -16920,7 +16908,7 @@
         <v>0</v>
       </c>
       <c r="AI115" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ115" t="n">
         <v>0</v>
@@ -17003,13 +16991,13 @@
         <v>191</v>
       </c>
       <c r="O116" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="P116" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="Q116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
         <v>0</v>
@@ -17033,19 +17021,19 @@
         <v>1</v>
       </c>
       <c r="Y116" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Z116" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="AA116" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="AB116" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="AC116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD116" t="n">
         <v>0</v>
@@ -17069,10 +17057,10 @@
         <v>1</v>
       </c>
       <c r="AK116" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AL116" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="AM116" t="n">
         <v>333</v>
@@ -17146,19 +17134,19 @@
         <v>189</v>
       </c>
       <c r="O117" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="P117" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="Q117" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
       <c r="S117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T117" t="n">
         <v>0</v>
@@ -17170,31 +17158,31 @@
         <v>0</v>
       </c>
       <c r="W117" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="X117" t="n">
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="Z117" t="n">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="AA117" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="AB117" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="AC117" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AD117" t="n">
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF117" t="n">
         <v>0</v>
@@ -17206,16 +17194,16 @@
         <v>0</v>
       </c>
       <c r="AI117" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AJ117" t="n">
         <v>0</v>
       </c>
       <c r="AK117" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AL117" t="n">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="AM117" t="n">
         <v>364</v>
@@ -17289,16 +17277,16 @@
         <v>211</v>
       </c>
       <c r="O118" t="n">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="P118" t="n">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="Q118" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -17319,22 +17307,22 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="Z118" t="n">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="AA118" t="n">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AB118" t="n">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="AC118" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE118" t="n">
         <v>0</v>
@@ -17355,10 +17343,10 @@
         <v>0</v>
       </c>
       <c r="AK118" t="n">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="AL118" t="n">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="AM118" t="n">
         <v>378</v>
@@ -17432,13 +17420,13 @@
         <v>325</v>
       </c>
       <c r="O119" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="P119" t="n">
-        <v>195</v>
+        <v>318</v>
       </c>
       <c r="Q119" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
         <v>0</v>
@@ -17462,19 +17450,19 @@
         <v>3</v>
       </c>
       <c r="Y119" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Z119" t="n">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="AA119" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AB119" t="n">
-        <v>195</v>
+        <v>318</v>
       </c>
       <c r="AC119" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
         <v>0</v>
@@ -17498,10 +17486,10 @@
         <v>3</v>
       </c>
       <c r="AK119" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AL119" t="n">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="AM119" t="n">
         <v>420</v>
@@ -17575,76 +17563,76 @@
         <v>162</v>
       </c>
       <c r="O120" t="n">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="P120" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q120" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R120" t="n">
+        <v>2</v>
+      </c>
+      <c r="S120" t="n">
+        <v>1</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="n">
         <v>3</v>
       </c>
-      <c r="S120" t="n">
-        <v>0</v>
-      </c>
-      <c r="T120" t="n">
+      <c r="V120" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" t="n">
+        <v>80</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>511</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>273</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>236</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>181</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD120" t="n">
         <v>2</v>
       </c>
-      <c r="U120" t="n">
-        <v>2</v>
-      </c>
-      <c r="V120" t="n">
-        <v>0</v>
-      </c>
-      <c r="W120" t="n">
-        <v>56</v>
-      </c>
-      <c r="X120" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y120" t="n">
-        <v>509</v>
-      </c>
-      <c r="Z120" t="n">
-        <v>250</v>
-      </c>
-      <c r="AA120" t="n">
-        <v>254</v>
-      </c>
-      <c r="AB120" t="n">
-        <v>169</v>
-      </c>
-      <c r="AC120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD120" t="n">
+      <c r="AE120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="n">
         <v>3</v>
       </c>
-      <c r="AE120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF120" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG120" t="n">
-        <v>2</v>
-      </c>
       <c r="AH120" t="n">
         <v>0</v>
       </c>
       <c r="AI120" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ120" t="n">
         <v>0</v>
       </c>
       <c r="AK120" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AL120" t="n">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="AM120" t="n">
         <v>430</v>
@@ -17718,19 +17706,19 @@
         <v>103</v>
       </c>
       <c r="O121" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P121" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="Q121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R121" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T121" t="n">
         <v>0</v>
@@ -17742,31 +17730,31 @@
         <v>0</v>
       </c>
       <c r="W121" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="X121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y121" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Z121" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="AA121" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AB121" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="AC121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD121" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF121" t="n">
         <v>0</v>
@@ -17778,16 +17766,16 @@
         <v>0</v>
       </c>
       <c r="AI121" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AJ121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK121" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AL121" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="AM121" t="n">
         <v>379</v>
@@ -17861,10 +17849,10 @@
         <v>156</v>
       </c>
       <c r="O122" t="n">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="P122" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="Q122" t="n">
         <v>2</v>
@@ -17873,7 +17861,7 @@
         <v>1</v>
       </c>
       <c r="S122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T122" t="n">
         <v>0</v>
@@ -17891,16 +17879,16 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Z122" t="n">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="AA122" t="n">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="AB122" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="AC122" t="n">
         <v>2</v>
@@ -17909,7 +17897,7 @@
         <v>1</v>
       </c>
       <c r="AE122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF122" t="n">
         <v>0</v>
@@ -17927,10 +17915,10 @@
         <v>0</v>
       </c>
       <c r="AK122" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AL122" t="n">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="AM122" t="n">
         <v>419</v>
@@ -18004,13 +17992,13 @@
         <v>154</v>
       </c>
       <c r="O123" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="P123" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="Q123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R123" t="n">
         <v>5</v>
@@ -18019,7 +18007,7 @@
         <v>1</v>
       </c>
       <c r="T123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -18037,16 +18025,16 @@
         <v>493</v>
       </c>
       <c r="Z123" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AA123" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="AB123" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="AC123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD123" t="n">
         <v>5</v>
@@ -18055,7 +18043,7 @@
         <v>1</v>
       </c>
       <c r="AF123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -18073,7 +18061,7 @@
         <v>493</v>
       </c>
       <c r="AL123" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AM123" t="n">
         <v>432</v>
@@ -18147,13 +18135,13 @@
         <v>170</v>
       </c>
       <c r="O124" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P124" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="Q124" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
         <v>4</v>
@@ -18177,19 +18165,19 @@
         <v>1</v>
       </c>
       <c r="Y124" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Z124" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AA124" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="AB124" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AC124" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD124" t="n">
         <v>4</v>
@@ -18213,10 +18201,10 @@
         <v>1</v>
       </c>
       <c r="AK124" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AL124" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="AM124" t="n">
         <v>437</v>
@@ -18290,19 +18278,19 @@
         <v>308</v>
       </c>
       <c r="O125" t="n">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="P125" t="n">
-        <v>128</v>
+        <v>225</v>
       </c>
       <c r="Q125" t="n">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T125" t="n">
         <v>0</v>
@@ -18320,25 +18308,25 @@
         <v>2</v>
       </c>
       <c r="Y125" t="n">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="Z125" t="n">
-        <v>266</v>
+        <v>319</v>
       </c>
       <c r="AA125" t="n">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="AB125" t="n">
-        <v>128</v>
+        <v>225</v>
       </c>
       <c r="AC125" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="AD125" t="n">
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF125" t="n">
         <v>0</v>
@@ -18356,10 +18344,10 @@
         <v>2</v>
       </c>
       <c r="AK125" t="n">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="AL125" t="n">
-        <v>265</v>
+        <v>319</v>
       </c>
       <c r="AM125" t="n">
         <v>303</v>
@@ -18433,10 +18421,10 @@
         <v>96</v>
       </c>
       <c r="O126" t="n">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="P126" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
@@ -18457,25 +18445,25 @@
         <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="X126" t="n">
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="Z126" t="n">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="AA126" t="n">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="AB126" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="AC126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD126" t="n">
         <v>0</v>
@@ -18493,16 +18481,16 @@
         <v>0</v>
       </c>
       <c r="AI126" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AJ126" t="n">
         <v>0</v>
       </c>
       <c r="AK126" t="n">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AL126" t="n">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="AM126" t="n">
         <v>366</v>
@@ -18576,16 +18564,16 @@
         <v>131</v>
       </c>
       <c r="O127" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="P127" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R127" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="S127" t="n">
         <v>2</v>
@@ -18606,22 +18594,22 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="Z127" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="AA127" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="AB127" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="AC127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD127" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -18642,10 +18630,10 @@
         <v>0</v>
       </c>
       <c r="AK127" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AL127" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="AM127" t="n">
         <v>394</v>
@@ -18722,13 +18710,13 @@
         <v>180</v>
       </c>
       <c r="P128" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="Q128" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="R128" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="S128" t="n">
         <v>2</v>
@@ -18743,7 +18731,7 @@
         <v>0</v>
       </c>
       <c r="W128" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="X128" t="n">
         <v>0</v>
@@ -18752,19 +18740,19 @@
         <v>470</v>
       </c>
       <c r="Z128" t="n">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="AA128" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AB128" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="AC128" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AD128" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -18779,7 +18767,7 @@
         <v>0</v>
       </c>
       <c r="AI128" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AJ128" t="n">
         <v>0</v>
@@ -18788,7 +18776,7 @@
         <v>470</v>
       </c>
       <c r="AL128" t="n">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="AM128" t="n">
         <v>372</v>
@@ -18862,13 +18850,13 @@
         <v>164</v>
       </c>
       <c r="O129" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="P129" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R129" t="n">
         <v>0</v>
@@ -18895,16 +18883,16 @@
         <v>345</v>
       </c>
       <c r="Z129" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="AA129" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="AB129" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD129" t="n">
         <v>0</v>
@@ -18931,7 +18919,7 @@
         <v>345</v>
       </c>
       <c r="AL129" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="AM129" t="n">
         <v>313</v>
@@ -19005,19 +18993,19 @@
         <v>223</v>
       </c>
       <c r="O130" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="P130" t="n">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="Q130" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="S130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T130" t="n">
         <v>0</v>
@@ -19035,25 +19023,25 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Z130" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="AA130" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="AB130" t="n">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="AC130" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="AD130" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AE130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF130" t="n">
         <v>0</v>
@@ -19071,10 +19059,10 @@
         <v>0</v>
       </c>
       <c r="AK130" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AL130" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="AM130" t="n">
         <v>386</v>
@@ -19148,13 +19136,13 @@
         <v>112</v>
       </c>
       <c r="O131" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="P131" t="n">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="Q131" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
         <v>1</v>
@@ -19172,7 +19160,7 @@
         <v>0</v>
       </c>
       <c r="W131" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="X131" t="n">
         <v>0</v>
@@ -19181,16 +19169,16 @@
         <v>399</v>
       </c>
       <c r="Z131" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AA131" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="AB131" t="n">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="AC131" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD131" t="n">
         <v>1</v>
@@ -19208,7 +19196,7 @@
         <v>0</v>
       </c>
       <c r="AI131" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="AJ131" t="n">
         <v>0</v>
@@ -19217,7 +19205,7 @@
         <v>399</v>
       </c>
       <c r="AL131" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AM131" t="n">
         <v>370</v>
@@ -19291,13 +19279,13 @@
         <v>170</v>
       </c>
       <c r="O132" t="n">
+        <v>182</v>
+      </c>
+      <c r="P132" t="n">
         <v>188</v>
       </c>
-      <c r="P132" t="n">
-        <v>189</v>
-      </c>
       <c r="Q132" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="R132" t="n">
         <v>0</v>
@@ -19315,25 +19303,25 @@
         <v>0</v>
       </c>
       <c r="W132" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="X132" t="n">
         <v>1</v>
       </c>
       <c r="Y132" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Z132" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="AA132" t="n">
+        <v>182</v>
+      </c>
+      <c r="AB132" t="n">
         <v>188</v>
       </c>
-      <c r="AB132" t="n">
-        <v>189</v>
-      </c>
       <c r="AC132" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AD132" t="n">
         <v>0</v>
@@ -19351,16 +19339,16 @@
         <v>0</v>
       </c>
       <c r="AI132" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AJ132" t="n">
         <v>1</v>
       </c>
       <c r="AK132" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AL132" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="AM132" t="n">
         <v>368</v>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_KESELURUHAN USAHA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_KESELURUHAN USAHA.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,242 +429,242 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Nama PCL</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Email PCL</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nama PML</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Email PML</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>nama_kec</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>koseka</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha Keluarga (ST2023 + UMKM)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>USAHA BKU - Ditemukan</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>USAHA BKU - Persentase Ditemukan</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>USAHA BKU - Baru</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>USAHA BKU - Persentase Baru</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>USAHA BKU - subtotal</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - Ditemukan​</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - Persentase Ditemukan​</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - Baru​</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - Persentase Baru​</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - subtotal​</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Total Usaha</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>APPROVED BY Pengawas</t>
         </is>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_KESELURUHAN USAHA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_KESELURUHAN USAHA.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,246 +413,246 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV132"/>
+  <dimension ref="A1:AV133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Nama PCL</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Email PCL</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nama PML</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Email PML</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>nama_kec</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>koseka</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha Keluarga (ST2023 + UMKM)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>USAHA BKU - Ditemukan</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>USAHA BKU - Persentase Ditemukan</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>USAHA BKU - Baru</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>USAHA BKU - Persentase Baru</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>USAHA BKU - subtotal</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - Ditemukan​</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - Persentase Ditemukan​</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - Baru​</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - Persentase Baru​</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - subtotal​</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Total Usaha</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>APPROVED BY Pengawas</t>
         </is>
@@ -813,19 +801,19 @@
         <v>447</v>
       </c>
       <c r="AR2" t="n">
-        <v>364</v>
+        <v>64</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AT2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="AU2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>4</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3">
@@ -1129,7 +1117,7 @@
         <v>342</v>
       </c>
       <c r="AR4" t="n">
-        <v>363</v>
+        <v>94</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -1141,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5">
@@ -1287,7 +1275,7 @@
         <v>249</v>
       </c>
       <c r="AR5" t="n">
-        <v>384</v>
+        <v>184</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
@@ -1296,10 +1284,10 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6">
@@ -1445,7 +1433,7 @@
         <v>233</v>
       </c>
       <c r="AR6" t="n">
-        <v>354</v>
+        <v>166</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
@@ -1457,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7">
@@ -1603,19 +1591,19 @@
         <v>395</v>
       </c>
       <c r="AR7" t="n">
-        <v>336</v>
+        <v>27</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AU7" t="n">
         <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8">
@@ -1761,19 +1749,19 @@
         <v>285</v>
       </c>
       <c r="AR8" t="n">
-        <v>304</v>
+        <v>85</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AT8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9">
@@ -1919,19 +1907,19 @@
         <v>389</v>
       </c>
       <c r="AR9" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -2077,19 +2065,19 @@
         <v>278</v>
       </c>
       <c r="AR10" t="n">
-        <v>324</v>
+        <v>141</v>
       </c>
       <c r="AS10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -2235,19 +2223,19 @@
         <v>271</v>
       </c>
       <c r="AR11" t="n">
-        <v>373</v>
+        <v>142</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>2</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12">
@@ -2393,19 +2381,19 @@
         <v>386</v>
       </c>
       <c r="AR12" t="n">
-        <v>383</v>
+        <v>104</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
         <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>1</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
@@ -2551,19 +2539,19 @@
         <v>493</v>
       </c>
       <c r="AR13" t="n">
-        <v>373</v>
+        <v>75</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AU13" t="n">
         <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14">
@@ -2709,19 +2697,19 @@
         <v>347</v>
       </c>
       <c r="AR14" t="n">
-        <v>364</v>
+        <v>74</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>3</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15">
@@ -2867,19 +2855,19 @@
         <v>308</v>
       </c>
       <c r="AR15" t="n">
-        <v>324</v>
+        <v>156</v>
       </c>
       <c r="AS15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AT15" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16">
@@ -3025,19 +3013,19 @@
         <v>382</v>
       </c>
       <c r="AR16" t="n">
-        <v>288</v>
+        <v>40</v>
       </c>
       <c r="AS16" t="n">
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17">
@@ -3075,7 +3063,7 @@
         <v>54</v>
       </c>
       <c r="H17" t="n">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="I17" t="n">
         <v>19</v>
@@ -3093,28 +3081,28 @@
         <v>33</v>
       </c>
       <c r="N17" t="n">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="O17" t="n">
-        <v>160.67</v>
+        <v>248.55</v>
       </c>
       <c r="P17" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="Q17" t="n">
-        <v>141.79</v>
+        <v>153.91</v>
       </c>
       <c r="R17" t="n">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="S17" t="n">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="T17" t="n">
         <v>71</v>
       </c>
       <c r="U17" t="n">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="V17" t="n">
         <v>2</v>
@@ -3135,22 +3123,22 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="AE17" t="n">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="AF17" t="n">
         <v>71</v>
       </c>
       <c r="AG17" t="n">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="AH17" t="n">
         <v>2</v>
@@ -3171,31 +3159,31 @@
         <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="AQ17" t="n">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="AR17" t="n">
-        <v>370</v>
+        <v>71</v>
       </c>
       <c r="AS17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AT17" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV17" t="n">
-        <v>1</v>
+        <v>410</v>
       </c>
     </row>
     <row r="18">
@@ -3341,19 +3329,19 @@
         <v>377</v>
       </c>
       <c r="AR18" t="n">
-        <v>366</v>
+        <v>45</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT18" t="n">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV18" t="n">
-        <v>3</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19">
@@ -3499,19 +3487,19 @@
         <v>318</v>
       </c>
       <c r="AR19" t="n">
-        <v>423</v>
+        <v>150</v>
       </c>
       <c r="AS19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
         <v>2</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20">
@@ -3657,19 +3645,19 @@
         <v>307</v>
       </c>
       <c r="AR20" t="n">
-        <v>284</v>
+        <v>15</v>
       </c>
       <c r="AS20" t="n">
         <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21">
@@ -3815,19 +3803,19 @@
         <v>253</v>
       </c>
       <c r="AR21" t="n">
-        <v>367</v>
+        <v>163</v>
       </c>
       <c r="AS21" t="n">
         <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV21" t="n">
-        <v>4</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22">
@@ -3862,58 +3850,58 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="H22" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>42.58</v>
+        <v>17.58</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L22" t="n">
-        <v>26.93</v>
+        <v>10.26</v>
       </c>
       <c r="M22" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N22" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="O22" t="n">
-        <v>144.91</v>
+        <v>153.89</v>
       </c>
       <c r="P22" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="Q22" t="n">
-        <v>185.58</v>
+        <v>218.27</v>
       </c>
       <c r="R22" t="n">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="S22" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="T22" t="n">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="U22" t="n">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -3925,31 +3913,31 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>531</v>
+        <v>488</v>
       </c>
       <c r="AE22" t="n">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="AF22" t="n">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="AG22" t="n">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="AH22" t="n">
         <v>1</v>
       </c>
       <c r="AI22" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="AJ22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -3961,31 +3949,31 @@
         <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>531</v>
+        <v>488</v>
       </c>
       <c r="AQ22" t="n">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="AR22" t="n">
-        <v>410</v>
+        <v>105</v>
       </c>
       <c r="AS22" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="AT22" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="n">
         <v>1</v>
       </c>
       <c r="AV22" t="n">
-        <v>22</v>
+        <v>299</v>
       </c>
     </row>
     <row r="23">
@@ -4131,19 +4119,19 @@
         <v>423</v>
       </c>
       <c r="AR23" t="n">
-        <v>450</v>
+        <v>141</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT23" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="AU23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24">
@@ -4289,19 +4277,19 @@
         <v>282</v>
       </c>
       <c r="AR24" t="n">
-        <v>359</v>
+        <v>137</v>
       </c>
       <c r="AS24" t="n">
         <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25">
@@ -4447,25 +4435,25 @@
         <v>368</v>
       </c>
       <c r="AR25" t="n">
-        <v>308</v>
+        <v>32</v>
       </c>
       <c r="AS25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>4</v>
+        <v>297</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>NaN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4494,58 +4482,58 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>269</v>
+        <v>47</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>9.58</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>31.58</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>116</v>
+        <v>29</v>
       </c>
       <c r="O26" t="n">
-        <v>355.57</v>
+        <v>58</v>
       </c>
       <c r="P26" t="n">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="Q26" t="n">
-        <v>303.28</v>
+        <v>40</v>
       </c>
       <c r="R26" t="n">
-        <v>222</v>
+        <v>49</v>
       </c>
       <c r="S26" t="n">
-        <v>236</v>
+        <v>50</v>
       </c>
       <c r="T26" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>211</v>
+        <v>50</v>
       </c>
       <c r="V26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -4557,31 +4545,31 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="AC26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD26" t="n">
-        <v>479</v>
+        <v>70</v>
       </c>
       <c r="AE26" t="n">
-        <v>309</v>
+        <v>70</v>
       </c>
       <c r="AF26" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>211</v>
+        <v>50</v>
       </c>
       <c r="AH26" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4593,31 +4581,31 @@
         <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="AO26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>479</v>
+        <v>70</v>
       </c>
       <c r="AQ26" t="n">
-        <v>307</v>
+        <v>70</v>
       </c>
       <c r="AR26" t="n">
-        <v>419</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
@@ -4763,19 +4751,19 @@
         <v>387</v>
       </c>
       <c r="AR27" t="n">
-        <v>342</v>
+        <v>56</v>
       </c>
       <c r="AS27" t="n">
         <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AU27" t="n">
         <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>3</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28">
@@ -4921,10 +4909,10 @@
         <v>375</v>
       </c>
       <c r="AR28" t="n">
-        <v>384</v>
+        <v>109</v>
       </c>
       <c r="AS28" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="AT28" t="n">
         <v>0</v>
@@ -4933,7 +4921,7 @@
         <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
     </row>
     <row r="29">
@@ -5079,19 +5067,19 @@
         <v>343</v>
       </c>
       <c r="AR29" t="n">
-        <v>357</v>
+        <v>133</v>
       </c>
       <c r="AS29" t="n">
         <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
     </row>
     <row r="30">
@@ -5237,19 +5225,19 @@
         <v>380</v>
       </c>
       <c r="AR30" t="n">
-        <v>457</v>
+        <v>139</v>
       </c>
       <c r="AS30" t="n">
         <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU30" t="n">
         <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31">
@@ -5395,19 +5383,19 @@
         <v>201</v>
       </c>
       <c r="AR31" t="n">
-        <v>315</v>
+        <v>3</v>
       </c>
       <c r="AS31" t="n">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="AT31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AU31" t="n">
         <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32">
@@ -5553,19 +5541,19 @@
         <v>281</v>
       </c>
       <c r="AR32" t="n">
-        <v>308</v>
+        <v>134</v>
       </c>
       <c r="AS32" t="n">
         <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33">
@@ -5711,19 +5699,19 @@
         <v>282</v>
       </c>
       <c r="AR33" t="n">
-        <v>365</v>
+        <v>156</v>
       </c>
       <c r="AS33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT33" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34">
@@ -5869,19 +5857,19 @@
         <v>450</v>
       </c>
       <c r="AR34" t="n">
-        <v>410</v>
+        <v>126</v>
       </c>
       <c r="AS34" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AT34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>425</v>
       </c>
     </row>
     <row r="35">
@@ -6027,19 +6015,19 @@
         <v>243</v>
       </c>
       <c r="AR35" t="n">
-        <v>303</v>
+        <v>131</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AU35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36">
@@ -6185,19 +6173,19 @@
         <v>477</v>
       </c>
       <c r="AR36" t="n">
-        <v>412</v>
+        <v>93</v>
       </c>
       <c r="AS36" t="n">
         <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>4</v>
+        <v>325</v>
       </c>
     </row>
     <row r="37">
@@ -6343,19 +6331,19 @@
         <v>518</v>
       </c>
       <c r="AR37" t="n">
-        <v>371</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
         <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
         <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>432</v>
       </c>
     </row>
     <row r="38">
@@ -6386,7 +6374,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6501,19 +6489,19 @@
         <v>365</v>
       </c>
       <c r="AR38" t="n">
-        <v>453</v>
+        <v>122</v>
       </c>
       <c r="AS38" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AT38" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>296</v>
       </c>
     </row>
     <row r="39">
@@ -6544,7 +6532,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6659,19 +6647,19 @@
         <v>313</v>
       </c>
       <c r="AR39" t="n">
-        <v>445</v>
+        <v>152</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AT39" t="n">
         <v>4</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
     </row>
     <row r="40">
@@ -6817,19 +6805,19 @@
         <v>399</v>
       </c>
       <c r="AR40" t="n">
-        <v>379</v>
+        <v>86</v>
       </c>
       <c r="AS40" t="n">
         <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
         <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
     </row>
     <row r="41">
@@ -6975,19 +6963,19 @@
         <v>350</v>
       </c>
       <c r="AR41" t="n">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="AS41" t="n">
         <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AU41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42">
@@ -7133,19 +7121,19 @@
         <v>387</v>
       </c>
       <c r="AR42" t="n">
-        <v>371</v>
+        <v>127</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU42" t="n">
         <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43">
@@ -7291,7 +7279,7 @@
         <v>388</v>
       </c>
       <c r="AR43" t="n">
-        <v>331</v>
+        <v>42</v>
       </c>
       <c r="AS43" t="n">
         <v>0</v>
@@ -7300,10 +7288,10 @@
         <v>13</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV43" t="n">
-        <v>1</v>
+        <v>319</v>
       </c>
     </row>
     <row r="44">
@@ -7449,7 +7437,7 @@
         <v>381</v>
       </c>
       <c r="AR44" t="n">
-        <v>301</v>
+        <v>12</v>
       </c>
       <c r="AS44" t="n">
         <v>0</v>
@@ -7458,254 +7446,254 @@
         <v>9</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV44" t="n">
-        <v>10</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Fitrianti Tadete</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>fitriantitadete68@gmail.com</t>
+          <t>fransiskapaolin@gmail.com</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Derlan Malawere</t>
+          <t>Yulianti Manambe</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>derlanmalawere92@gmail.com</t>
+          <t>anthymanambe8@gmail.com</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(092) TAHUNA BARAT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H45" t="n">
-        <v>389</v>
+        <v>429</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J45" t="n">
-        <v>1.47</v>
+        <v>22.87</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>1.47</v>
+        <v>3.7</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N45" t="n">
-        <v>190</v>
+        <v>146</v>
       </c>
       <c r="O45" t="n">
-        <v>311.89</v>
+        <v>519.47</v>
       </c>
       <c r="P45" t="n">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="Q45" t="n">
-        <v>185.17</v>
+        <v>153.96</v>
       </c>
       <c r="R45" t="n">
-        <v>303</v>
+        <v>191</v>
       </c>
       <c r="S45" t="n">
-        <v>305</v>
+        <v>199</v>
       </c>
       <c r="T45" t="n">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="U45" t="n">
-        <v>329</v>
+        <v>236</v>
       </c>
       <c r="V45" t="n">
         <v>1</v>
       </c>
       <c r="W45" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD45" t="n">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="AE45" t="n">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="AF45" t="n">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AG45" t="n">
-        <v>329</v>
+        <v>236</v>
       </c>
       <c r="AH45" t="n">
         <v>1</v>
       </c>
       <c r="AI45" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK45" t="n">
         <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM45" t="n">
         <v>0</v>
       </c>
       <c r="AN45" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="AO45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AP45" t="n">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="AQ45" t="n">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="AR45" t="n">
-        <v>355</v>
+        <v>146</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV45" t="n">
-        <v>2</v>
+        <v>236</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>fransiskapaolin@gmail.com</t>
+          <t>frzfrz130293@gmail.com</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yulianti Manambe</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>anthymanambe8@gmail.com</t>
+          <t>yanfwpadang84@gmail.com</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(092) TAHUNA BARAT</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="H46" t="n">
-        <v>429</v>
+        <v>174</v>
       </c>
       <c r="I46" t="n">
+        <v>19</v>
+      </c>
+      <c r="J46" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="K46" t="n">
         <v>7</v>
       </c>
-      <c r="J46" t="n">
-        <v>22.87</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1</v>
-      </c>
       <c r="L46" t="n">
-        <v>3.7</v>
+        <v>58.81</v>
       </c>
       <c r="M46" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="N46" t="n">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="O46" t="n">
-        <v>519.47</v>
+        <v>341.08</v>
       </c>
       <c r="P46" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="Q46" t="n">
-        <v>153.96</v>
+        <v>47.62</v>
       </c>
       <c r="R46" t="n">
-        <v>191</v>
+        <v>44</v>
       </c>
       <c r="S46" t="n">
-        <v>199</v>
+        <v>70</v>
       </c>
       <c r="T46" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="U46" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="V46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="X46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
         <v>0</v>
@@ -7717,31 +7705,31 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="AC46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>477</v>
+        <v>433</v>
       </c>
       <c r="AE46" t="n">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="AF46" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="AG46" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AH46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="AJ46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
         <v>0</v>
@@ -7753,311 +7741,311 @@
         <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="AO46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>477</v>
+        <v>432</v>
       </c>
       <c r="AQ46" t="n">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="AR46" t="n">
-        <v>434</v>
+        <v>132</v>
       </c>
       <c r="AS46" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="AT46" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AU46" t="n">
         <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>frzfrz130293@gmail.com</t>
+          <t>geovanimonok34@gmail.com</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>B. Lenskar Diamanis</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>yanfwpadang84@gmail.com</t>
+          <t>lenskardiamaniz@gmail.com</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(080) MANGANITU</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="H47" t="n">
-        <v>174</v>
+        <v>309</v>
       </c>
       <c r="I47" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
-        <v>152.5</v>
+        <v>38.78</v>
       </c>
       <c r="K47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>58.81</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>37</v>
+        <v>110</v>
       </c>
       <c r="O47" t="n">
-        <v>341.08</v>
+        <v>226.2</v>
       </c>
       <c r="P47" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="Q47" t="n">
-        <v>47.62</v>
+        <v>135.01</v>
       </c>
       <c r="R47" t="n">
-        <v>44</v>
+        <v>179</v>
       </c>
       <c r="S47" t="n">
-        <v>70</v>
+        <v>183</v>
       </c>
       <c r="T47" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="U47" t="n">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="W47" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y47" t="n">
         <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="AE47" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="AF47" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="AG47" t="n">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AI47" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK47" t="n">
         <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
         <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="AQ47" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="AR47" t="n">
-        <v>375</v>
+        <v>128</v>
       </c>
       <c r="AS47" t="n">
         <v>1</v>
       </c>
       <c r="AT47" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>geovanimonok34@gmail.com</t>
+          <t>ghenovhepaparaso@gmail.com</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B. Lenskar Diamanis</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>lenskardiamaniz@gmail.com</t>
+          <t>ferdinandtangkabiringan@gmail.com</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>(080) MANGANITU</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>27</v>
+        <v>209</v>
       </c>
       <c r="H48" t="n">
-        <v>309</v>
+        <v>36</v>
       </c>
       <c r="I48" t="n">
+        <v>54</v>
+      </c>
+      <c r="J48" t="n">
+        <v>76.69</v>
+      </c>
+      <c r="K48" t="n">
+        <v>39</v>
+      </c>
+      <c r="L48" t="n">
+        <v>55.89</v>
+      </c>
+      <c r="M48" t="n">
+        <v>93</v>
+      </c>
+      <c r="N48" t="n">
+        <v>17</v>
+      </c>
+      <c r="O48" t="n">
+        <v>41.43</v>
+      </c>
+      <c r="P48" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>125.98</v>
+      </c>
+      <c r="R48" t="n">
+        <v>59</v>
+      </c>
+      <c r="S48" t="n">
+        <v>152</v>
+      </c>
+      <c r="T48" t="n">
+        <v>121</v>
+      </c>
+      <c r="U48" t="n">
+        <v>334</v>
+      </c>
+      <c r="V48" t="n">
         <v>4</v>
       </c>
-      <c r="J48" t="n">
-        <v>38.78</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>485</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>364</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>121</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>334</v>
+      </c>
+      <c r="AH48" t="n">
         <v>4</v>
       </c>
-      <c r="N48" t="n">
-        <v>110</v>
-      </c>
-      <c r="O48" t="n">
-        <v>226.2</v>
-      </c>
-      <c r="P48" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>135.01</v>
-      </c>
-      <c r="R48" t="n">
-        <v>179</v>
-      </c>
-      <c r="S48" t="n">
-        <v>183</v>
-      </c>
-      <c r="T48" t="n">
-        <v>128</v>
-      </c>
-      <c r="U48" t="n">
-        <v>218</v>
-      </c>
-      <c r="V48" t="n">
-        <v>35</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1</v>
-      </c>
-      <c r="X48" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>42</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>428</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>299</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>128</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>218</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>35</v>
-      </c>
       <c r="AI48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
         <v>0</v>
@@ -8069,19 +8057,19 @@
         <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AO48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP48" t="n">
-        <v>428</v>
+        <v>485</v>
       </c>
       <c r="AQ48" t="n">
-        <v>299</v>
+        <v>364</v>
       </c>
       <c r="AR48" t="n">
-        <v>363</v>
+        <v>121</v>
       </c>
       <c r="AS48" t="n">
         <v>0</v>
@@ -8090,567 +8078,567 @@
         <v>4</v>
       </c>
       <c r="AU48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ghenovhepaparaso@gmail.com</t>
+          <t>gracedorongpangalo11@gmail.com</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Fiane Greti Mansauda</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ferdinandtangkabiringan@gmail.com</t>
+          <t>fianemansauda89@gmail.com</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(070) TABUKAN TENGAH</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>209</v>
+        <v>27</v>
       </c>
       <c r="H49" t="n">
-        <v>36</v>
+        <v>478</v>
       </c>
       <c r="I49" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="J49" t="n">
-        <v>76.69</v>
+        <v>5.98</v>
       </c>
       <c r="K49" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="L49" t="n">
-        <v>55.89</v>
+        <v>12.44</v>
       </c>
       <c r="M49" t="n">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="N49" t="n">
-        <v>17</v>
+        <v>196</v>
       </c>
       <c r="O49" t="n">
-        <v>41.43</v>
+        <v>341.52</v>
       </c>
       <c r="P49" t="n">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="Q49" t="n">
-        <v>125.98</v>
+        <v>240.08</v>
       </c>
       <c r="R49" t="n">
-        <v>59</v>
+        <v>300</v>
       </c>
       <c r="S49" t="n">
-        <v>152</v>
+        <v>316</v>
       </c>
       <c r="T49" t="n">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="U49" t="n">
-        <v>334</v>
+        <v>242</v>
       </c>
       <c r="V49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W49" t="n">
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y49" t="n">
         <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AC49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD49" t="n">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="AE49" t="n">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="AF49" t="n">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="AG49" t="n">
-        <v>334</v>
+        <v>242</v>
       </c>
       <c r="AH49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AK49" t="n">
         <v>0</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM49" t="n">
         <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AO49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP49" t="n">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="AQ49" t="n">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="AR49" t="n">
-        <v>411</v>
+        <v>178</v>
       </c>
       <c r="AS49" t="n">
         <v>0</v>
       </c>
       <c r="AT49" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Grees Pangandaheng</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>gracedorongpangalo11@gmail.com</t>
+          <t>greispangandaheng@gmail.com</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>Novdein Arif Bongkitang</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>fianemansauda89@gmail.com</t>
+          <t>novdeinarifbongkitang@gmail.com</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(070) TABUKAN TENGAH</t>
+          <t>(050) TAMAKO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="H50" t="n">
-        <v>478</v>
+        <v>282</v>
       </c>
       <c r="I50" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>5.98</v>
+        <v>2.05</v>
       </c>
       <c r="K50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L50" t="n">
-        <v>12.44</v>
+        <v>9.51</v>
       </c>
       <c r="M50" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="N50" t="n">
-        <v>196</v>
+        <v>139</v>
       </c>
       <c r="O50" t="n">
-        <v>341.52</v>
+        <v>174.63</v>
       </c>
       <c r="P50" t="n">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="Q50" t="n">
-        <v>240.08</v>
+        <v>213.81</v>
       </c>
       <c r="R50" t="n">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="S50" t="n">
-        <v>316</v>
+        <v>295</v>
       </c>
       <c r="T50" t="n">
-        <v>178</v>
+        <v>61</v>
       </c>
       <c r="U50" t="n">
-        <v>242</v>
+        <v>398</v>
       </c>
       <c r="V50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="X50" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Y50" t="n">
         <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="AC50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>476</v>
+        <v>539</v>
       </c>
       <c r="AE50" t="n">
-        <v>298</v>
+        <v>460</v>
       </c>
       <c r="AF50" t="n">
-        <v>178</v>
+        <v>61</v>
       </c>
       <c r="AG50" t="n">
-        <v>242</v>
+        <v>398</v>
       </c>
       <c r="AH50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AJ50" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AK50" t="n">
         <v>0</v>
       </c>
       <c r="AL50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM50" t="n">
         <v>0</v>
       </c>
       <c r="AN50" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="AO50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>476</v>
+        <v>539</v>
       </c>
       <c r="AQ50" t="n">
-        <v>298</v>
+        <v>460</v>
       </c>
       <c r="AR50" t="n">
-        <v>372</v>
+        <v>61</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AT50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Grees Pangandaheng</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>greispangandaheng@gmail.com</t>
+          <t>hamendahasrita@gmail.com</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Novdein Arif Bongkitang</t>
+          <t>Novrilley Richard Mumu</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>novdeinarifbongkitang@gmail.com</t>
+          <t>novrilleymumu11@gmail.com</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(050) TAMAKO</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="G51" t="n">
+        <v>32</v>
+      </c>
+      <c r="H51" t="n">
+        <v>346</v>
+      </c>
+      <c r="I51" t="n">
+        <v>9</v>
+      </c>
+      <c r="J51" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="K51" t="n">
+        <v>5</v>
+      </c>
+      <c r="L51" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="M51" t="n">
+        <v>14</v>
+      </c>
+      <c r="N51" t="n">
+        <v>197</v>
+      </c>
+      <c r="O51" t="n">
+        <v>267.06</v>
+      </c>
+      <c r="P51" t="n">
+        <v>172</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>211.37</v>
+      </c>
+      <c r="R51" t="n">
+        <v>369</v>
+      </c>
+      <c r="S51" t="n">
+        <v>383</v>
+      </c>
+      <c r="T51" t="n">
+        <v>89</v>
+      </c>
+      <c r="U51" t="n">
+        <v>331</v>
+      </c>
+      <c r="V51" t="n">
         <v>8</v>
       </c>
-      <c r="H51" t="n">
-        <v>282</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="K51" t="n">
-        <v>9</v>
-      </c>
-      <c r="L51" t="n">
-        <v>9.51</v>
-      </c>
-      <c r="M51" t="n">
-        <v>11</v>
-      </c>
-      <c r="N51" t="n">
-        <v>139</v>
-      </c>
-      <c r="O51" t="n">
-        <v>174.63</v>
-      </c>
-      <c r="P51" t="n">
-        <v>145</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>213.81</v>
-      </c>
-      <c r="R51" t="n">
-        <v>284</v>
-      </c>
-      <c r="S51" t="n">
-        <v>295</v>
-      </c>
-      <c r="T51" t="n">
-        <v>61</v>
-      </c>
-      <c r="U51" t="n">
-        <v>398</v>
-      </c>
-      <c r="V51" t="n">
-        <v>7</v>
-      </c>
       <c r="W51" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>482</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>390</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>89</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>331</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI51" t="n">
         <v>3</v>
       </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>52</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>539</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>460</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>61</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>398</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>18</v>
-      </c>
       <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>482</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>390</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>89</v>
+      </c>
+      <c r="AS51" t="n">
         <v>3</v>
       </c>
-      <c r="AK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>52</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>539</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>460</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>395</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0</v>
-      </c>
       <c r="AT51" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="AU51" t="n">
         <v>0</v>
       </c>
       <c r="AV51" t="n">
-        <v>0</v>
+        <v>331</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>hamendahasrita@gmail.com</t>
+          <t>hapitudhy@gmail.com</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Novrilley Richard Mumu</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>novrilleymumu11@gmail.com</t>
+          <t>vonnelariunaung77560@gmail.com</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="H52" t="n">
-        <v>346</v>
+        <v>191</v>
       </c>
       <c r="I52" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J52" t="n">
-        <v>16.32</v>
+        <v>24.85</v>
       </c>
       <c r="K52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L52" t="n">
-        <v>5.24</v>
+        <v>7.44</v>
       </c>
       <c r="M52" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N52" t="n">
-        <v>197</v>
+        <v>110</v>
       </c>
       <c r="O52" t="n">
-        <v>267.06</v>
+        <v>180.92</v>
       </c>
       <c r="P52" t="n">
-        <v>172</v>
+        <v>119</v>
       </c>
       <c r="Q52" t="n">
-        <v>211.37</v>
+        <v>186.79</v>
       </c>
       <c r="R52" t="n">
-        <v>369</v>
+        <v>229</v>
       </c>
       <c r="S52" t="n">
-        <v>383</v>
+        <v>245</v>
       </c>
       <c r="T52" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="U52" t="n">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="V52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="X52" t="n">
         <v>0</v>
@@ -8659,34 +8647,34 @@
         <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="AC52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="AE52" t="n">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="AF52" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="AG52" t="n">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="AH52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AJ52" t="n">
         <v>0</v>
@@ -8695,28 +8683,28 @@
         <v>0</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM52" t="n">
         <v>0</v>
       </c>
       <c r="AN52" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="AO52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="AQ52" t="n">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="AR52" t="n">
-        <v>378</v>
+        <v>104</v>
       </c>
       <c r="AS52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AT52" t="n">
         <v>0</v>
@@ -8725,28 +8713,28 @@
         <v>0</v>
       </c>
       <c r="AV52" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>hapitudhy@gmail.com</t>
+          <t>harilamachris23@gmail.com</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>vonnelariunaung77560@gmail.com</t>
+          <t>jeniemonok7@gmail.com</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -8760,219 +8748,219 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H53" t="n">
-        <v>181</v>
+        <v>326</v>
       </c>
       <c r="I53" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J53" t="n">
-        <v>26.57</v>
+        <v>36.22</v>
       </c>
       <c r="K53" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L53" t="n">
-        <v>8.449999999999999</v>
+        <v>42.22</v>
       </c>
       <c r="M53" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N53" t="n">
-        <v>85</v>
+        <v>154</v>
       </c>
       <c r="O53" t="n">
-        <v>194.89</v>
+        <v>427.77</v>
       </c>
       <c r="P53" t="n">
-        <v>141</v>
+        <v>95</v>
       </c>
       <c r="Q53" t="n">
-        <v>270.09</v>
+        <v>293.78</v>
       </c>
       <c r="R53" t="n">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="S53" t="n">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="T53" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="U53" t="n">
-        <v>341</v>
+        <v>219</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W53" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y53" t="n">
         <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD53" t="n">
-        <v>493</v>
+        <v>452</v>
       </c>
       <c r="AE53" t="n">
-        <v>382</v>
+        <v>279</v>
       </c>
       <c r="AF53" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="AG53" t="n">
-        <v>341</v>
+        <v>219</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI53" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AK53" t="n">
         <v>0</v>
       </c>
       <c r="AL53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM53" t="n">
         <v>0</v>
       </c>
       <c r="AN53" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="AO53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP53" t="n">
-        <v>493</v>
+        <v>452</v>
       </c>
       <c r="AQ53" t="n">
-        <v>382</v>
+        <v>279</v>
       </c>
       <c r="AR53" t="n">
-        <v>429</v>
+        <v>150</v>
       </c>
       <c r="AS53" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="AT53" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AU53" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AV53" t="n">
-        <v>1</v>
+        <v>219</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>harilamachris23@gmail.com</t>
+          <t>hshyntike@gmail.com</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Ningsi Karendehi</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jeniemonok7@gmail.com</t>
+          <t>ningsikarendehi968@gmail.com</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(061) TABUKAN SELATAN TENGAH &amp; (062) TABUKAN SELATAN TENGGARA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erwin &amp; Lalu</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="H54" t="n">
-        <v>274</v>
+        <v>372</v>
       </c>
       <c r="I54" t="n">
+        <v>2</v>
+      </c>
+      <c r="J54" t="n">
+        <v>5.640000000000001</v>
+      </c>
+      <c r="K54" t="n">
         <v>7</v>
       </c>
-      <c r="J54" t="n">
-        <v>42.89</v>
-      </c>
-      <c r="K54" t="n">
-        <v>2</v>
-      </c>
       <c r="L54" t="n">
-        <v>22.22</v>
+        <v>20.04</v>
       </c>
       <c r="M54" t="n">
         <v>9</v>
       </c>
       <c r="N54" t="n">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="O54" t="n">
-        <v>347.77</v>
+        <v>357.02</v>
       </c>
       <c r="P54" t="n">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="Q54" t="n">
-        <v>287.11</v>
+        <v>317.3</v>
       </c>
       <c r="R54" t="n">
-        <v>204</v>
+        <v>272</v>
       </c>
       <c r="S54" t="n">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="T54" t="n">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="U54" t="n">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="V54" t="n">
         <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -8981,34 +8969,34 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD54" t="n">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="AE54" t="n">
-        <v>201</v>
+        <v>317</v>
       </c>
       <c r="AF54" t="n">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="AG54" t="n">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="AH54" t="n">
         <v>0</v>
       </c>
       <c r="AI54" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9017,120 +9005,120 @@
         <v>0</v>
       </c>
       <c r="AN54" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="AO54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP54" t="n">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="AQ54" t="n">
-        <v>201</v>
+        <v>317</v>
       </c>
       <c r="AR54" t="n">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="AS54" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AT54" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AU54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV54" t="n">
-        <v>2</v>
+        <v>235</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>hshyntike@gmail.com</t>
+          <t>igirisatia5@gmail.com</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ningsi Karendehi</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ningsikarendehi968@gmail.com</t>
+          <t>yanfwpadang84@gmail.com</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(061) TABUKAN SELATAN TENGAH &amp; (062) TABUKAN SELATAN TENGGARA</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Erwin &amp; Lalu</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="H55" t="n">
-        <v>372</v>
+        <v>80</v>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J55" t="n">
-        <v>5.640000000000001</v>
+        <v>42.99</v>
       </c>
       <c r="K55" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="L55" t="n">
-        <v>20.04</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="N55" t="n">
-        <v>147</v>
+        <v>31</v>
       </c>
       <c r="O55" t="n">
-        <v>357.02</v>
+        <v>81.92</v>
       </c>
       <c r="P55" t="n">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="Q55" t="n">
-        <v>317.3</v>
+        <v>194.79</v>
       </c>
       <c r="R55" t="n">
-        <v>272</v>
+        <v>97</v>
       </c>
       <c r="S55" t="n">
-        <v>281</v>
+        <v>142</v>
       </c>
       <c r="T55" t="n">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="U55" t="n">
-        <v>235</v>
+        <v>403</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="X55" t="n">
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -9139,34 +9127,34 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="AC55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD55" t="n">
-        <v>400</v>
+        <v>636</v>
       </c>
       <c r="AE55" t="n">
-        <v>317</v>
+        <v>431</v>
       </c>
       <c r="AF55" t="n">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="AG55" t="n">
-        <v>235</v>
+        <v>403</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AJ55" t="n">
         <v>0</v>
       </c>
       <c r="AK55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9175,117 +9163,117 @@
         <v>0</v>
       </c>
       <c r="AN55" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="AO55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP55" t="n">
-        <v>400</v>
+        <v>636</v>
       </c>
       <c r="AQ55" t="n">
-        <v>317</v>
+        <v>431</v>
       </c>
       <c r="AR55" t="n">
-        <v>279</v>
+        <v>160</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT55" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AU55" t="n">
         <v>0</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>403</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>igirisatia5@gmail.com</t>
+          <t>indrydorthea@gmail.com</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>yanfwpadang84@gmail.com</t>
+          <t>jekirvenkildompas@gmail.com</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(070) TABUKAN TENGAH</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="H56" t="n">
-        <v>80</v>
+        <v>548</v>
       </c>
       <c r="I56" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J56" t="n">
-        <v>42.99</v>
+        <v>5.64</v>
       </c>
       <c r="K56" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="L56" t="n">
-        <v>80.29000000000001</v>
+        <v>15.11</v>
       </c>
       <c r="M56" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="N56" t="n">
-        <v>31</v>
+        <v>160</v>
       </c>
       <c r="O56" t="n">
-        <v>81.92</v>
+        <v>265.39</v>
       </c>
       <c r="P56" t="n">
-        <v>66</v>
+        <v>191</v>
       </c>
       <c r="Q56" t="n">
-        <v>194.79</v>
+        <v>313.86</v>
       </c>
       <c r="R56" t="n">
-        <v>97</v>
+        <v>351</v>
       </c>
       <c r="S56" t="n">
-        <v>142</v>
+        <v>365</v>
       </c>
       <c r="T56" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="U56" t="n">
-        <v>403</v>
+        <v>215</v>
       </c>
       <c r="V56" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="W56" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y56" t="n">
         <v>0</v>
@@ -9297,31 +9285,31 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="AC56" t="n">
         <v>1</v>
       </c>
       <c r="AD56" t="n">
-        <v>636</v>
+        <v>493</v>
       </c>
       <c r="AE56" t="n">
-        <v>431</v>
+        <v>328</v>
       </c>
       <c r="AF56" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="AG56" t="n">
-        <v>403</v>
+        <v>215</v>
       </c>
       <c r="AH56" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="AI56" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK56" t="n">
         <v>0</v>
@@ -9333,117 +9321,117 @@
         <v>0</v>
       </c>
       <c r="AN56" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="AO56" t="n">
         <v>1</v>
       </c>
       <c r="AP56" t="n">
-        <v>636</v>
+        <v>493</v>
       </c>
       <c r="AQ56" t="n">
-        <v>431</v>
+        <v>328</v>
       </c>
       <c r="AR56" t="n">
-        <v>420</v>
+        <v>148</v>
       </c>
       <c r="AS56" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AT56" t="n">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="AU56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV56" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>indrydorthea@gmail.com</t>
+          <t>iyanmaniku1@gmail.com</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Derlan Malawere</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jekirvenkildompas@gmail.com</t>
+          <t>derlanmalawere92@gmail.com</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(070) TABUKAN TENGAH</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H57" t="n">
-        <v>548</v>
+        <v>389</v>
       </c>
       <c r="I57" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
-        <v>5.64</v>
+        <v>1.47</v>
       </c>
       <c r="K57" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>15.11</v>
+        <v>1.47</v>
       </c>
       <c r="M57" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="N57" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="O57" t="n">
-        <v>265.39</v>
+        <v>311.89</v>
       </c>
       <c r="P57" t="n">
-        <v>191</v>
+        <v>113</v>
       </c>
       <c r="Q57" t="n">
-        <v>313.86</v>
+        <v>185.17</v>
       </c>
       <c r="R57" t="n">
-        <v>351</v>
+        <v>303</v>
       </c>
       <c r="S57" t="n">
-        <v>365</v>
+        <v>305</v>
       </c>
       <c r="T57" t="n">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="U57" t="n">
-        <v>215</v>
+        <v>329</v>
       </c>
       <c r="V57" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="W57" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="X57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
         <v>0</v>
@@ -9455,31 +9443,31 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="AC57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="AE57" t="n">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AF57" t="n">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="AG57" t="n">
-        <v>215</v>
+        <v>329</v>
       </c>
       <c r="AH57" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="AI57" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AJ57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK57" t="n">
         <v>0</v>
@@ -9491,31 +9479,31 @@
         <v>0</v>
       </c>
       <c r="AN57" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="AO57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="AQ57" t="n">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AR57" t="n">
-        <v>336</v>
+        <v>85</v>
       </c>
       <c r="AS57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT57" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AU57" t="n">
         <v>0</v>
       </c>
       <c r="AV57" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
     </row>
     <row r="58">
@@ -9661,19 +9649,19 @@
         <v>267</v>
       </c>
       <c r="AR58" t="n">
-        <v>363</v>
+        <v>194</v>
       </c>
       <c r="AS58" t="n">
         <v>0</v>
       </c>
       <c r="AT58" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AU58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV58" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
     </row>
     <row r="59">
@@ -9819,19 +9807,19 @@
         <v>364</v>
       </c>
       <c r="AR59" t="n">
-        <v>383</v>
+        <v>108</v>
       </c>
       <c r="AS59" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AT59" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AU59" t="n">
         <v>0</v>
       </c>
       <c r="AV59" t="n">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="60">
@@ -9977,19 +9965,19 @@
         <v>289</v>
       </c>
       <c r="AR60" t="n">
-        <v>377</v>
+        <v>160</v>
       </c>
       <c r="AS60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT60" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="AU60" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AV60" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
     </row>
     <row r="61">
@@ -10135,19 +10123,19 @@
         <v>238</v>
       </c>
       <c r="AR61" t="n">
-        <v>314</v>
+        <v>126</v>
       </c>
       <c r="AS61" t="n">
         <v>0</v>
       </c>
       <c r="AT61" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AU61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV61" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62">
@@ -10293,19 +10281,19 @@
         <v>440</v>
       </c>
       <c r="AR62" t="n">
-        <v>365</v>
+        <v>79</v>
       </c>
       <c r="AS62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT62" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="AU62" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AV62" t="n">
-        <v>6</v>
+        <v>345</v>
       </c>
     </row>
     <row r="63">
@@ -10451,19 +10439,19 @@
         <v>373</v>
       </c>
       <c r="AR63" t="n">
-        <v>324</v>
+        <v>99</v>
       </c>
       <c r="AS63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT63" t="n">
         <v>0</v>
       </c>
       <c r="AU63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV63" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64">
@@ -10609,19 +10597,19 @@
         <v>394</v>
       </c>
       <c r="AR64" t="n">
-        <v>440</v>
+        <v>157</v>
       </c>
       <c r="AS64" t="n">
         <v>0</v>
       </c>
       <c r="AT64" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AU64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV64" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="65">
@@ -10767,19 +10755,19 @@
         <v>357</v>
       </c>
       <c r="AR65" t="n">
-        <v>417</v>
+        <v>105</v>
       </c>
       <c r="AS65" t="n">
         <v>0</v>
       </c>
       <c r="AT65" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AU65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV65" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
     </row>
     <row r="66">
@@ -10925,19 +10913,19 @@
         <v>397</v>
       </c>
       <c r="AR66" t="n">
-        <v>384</v>
+        <v>78</v>
       </c>
       <c r="AS66" t="n">
         <v>0</v>
       </c>
       <c r="AT66" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="AU66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV66" t="n">
-        <v>2</v>
+        <v>316</v>
       </c>
     </row>
     <row r="67">
@@ -11083,19 +11071,19 @@
         <v>255</v>
       </c>
       <c r="AR67" t="n">
-        <v>297</v>
+        <v>100</v>
       </c>
       <c r="AS67" t="n">
         <v>0</v>
       </c>
       <c r="AT67" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AU67" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AV67" t="n">
-        <v>1</v>
+        <v>185</v>
       </c>
     </row>
     <row r="68">
@@ -11241,19 +11229,19 @@
         <v>504</v>
       </c>
       <c r="AR68" t="n">
-        <v>395</v>
+        <v>21</v>
       </c>
       <c r="AS68" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AT68" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AU68" t="n">
         <v>1</v>
       </c>
       <c r="AV68" t="n">
-        <v>8</v>
+        <v>448</v>
       </c>
     </row>
     <row r="69">
@@ -11399,19 +11387,19 @@
         <v>300</v>
       </c>
       <c r="AR69" t="n">
-        <v>317</v>
+        <v>101</v>
       </c>
       <c r="AS69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="AU69" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AV69" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70">
@@ -11557,19 +11545,19 @@
         <v>224</v>
       </c>
       <c r="AR70" t="n">
-        <v>306</v>
+        <v>131</v>
       </c>
       <c r="AS70" t="n">
         <v>0</v>
       </c>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU70" t="n">
         <v>0</v>
       </c>
       <c r="AV70" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
     </row>
     <row r="71">
@@ -11715,19 +11703,19 @@
         <v>441</v>
       </c>
       <c r="AR71" t="n">
-        <v>366</v>
+        <v>80</v>
       </c>
       <c r="AS71" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU71" t="n">
         <v>0</v>
       </c>
       <c r="AV71" t="n">
-        <v>0</v>
+        <v>391</v>
       </c>
     </row>
     <row r="72">
@@ -11873,19 +11861,19 @@
         <v>578</v>
       </c>
       <c r="AR72" t="n">
-        <v>353</v>
+        <v>3</v>
       </c>
       <c r="AS72" t="n">
         <v>0</v>
       </c>
       <c r="AT72" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AU72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV72" t="n">
-        <v>0</v>
+        <v>492</v>
       </c>
     </row>
     <row r="73">
@@ -12031,19 +12019,19 @@
         <v>331</v>
       </c>
       <c r="AR73" t="n">
-        <v>362</v>
+        <v>105</v>
       </c>
       <c r="AS73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT73" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AU73" t="n">
         <v>0</v>
       </c>
       <c r="AV73" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
     </row>
     <row r="74">
@@ -12189,10 +12177,10 @@
         <v>472</v>
       </c>
       <c r="AR74" t="n">
-        <v>398</v>
+        <v>19</v>
       </c>
       <c r="AS74" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="AT74" t="n">
         <v>0</v>
@@ -12201,7 +12189,7 @@
         <v>0</v>
       </c>
       <c r="AV74" t="n">
-        <v>0</v>
+        <v>386</v>
       </c>
     </row>
     <row r="75">
@@ -12347,19 +12335,19 @@
         <v>283</v>
       </c>
       <c r="AR75" t="n">
-        <v>359</v>
+        <v>138</v>
       </c>
       <c r="AS75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AT75" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AU75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV75" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="76">
@@ -12505,19 +12493,19 @@
         <v>251</v>
       </c>
       <c r="AR76" t="n">
-        <v>357</v>
+        <v>175</v>
       </c>
       <c r="AS76" t="n">
         <v>0</v>
       </c>
       <c r="AT76" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="AU76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV76" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77">
@@ -12663,19 +12651,19 @@
         <v>430</v>
       </c>
       <c r="AR77" t="n">
-        <v>386</v>
+        <v>87</v>
       </c>
       <c r="AS77" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="AT77" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AU77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV77" t="n">
-        <v>7</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78">
@@ -12821,19 +12809,19 @@
         <v>306</v>
       </c>
       <c r="AR78" t="n">
-        <v>350</v>
+        <v>114</v>
       </c>
       <c r="AS78" t="n">
         <v>0</v>
       </c>
       <c r="AT78" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="AU78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV78" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="79">
@@ -12979,7 +12967,7 @@
         <v>394</v>
       </c>
       <c r="AR79" t="n">
-        <v>319</v>
+        <v>21</v>
       </c>
       <c r="AS79" t="n">
         <v>0</v>
@@ -12988,168 +12976,168 @@
         <v>6</v>
       </c>
       <c r="AU79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV79" t="n">
-        <v>7</v>
+        <v>313</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Mery Grace Anabelia Kantohe</t>
+          <t>Aldo Jhon Mesak Bangonang</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>merykantohe979@gmail.com</t>
+          <t>mesakbangonang99@gmail.com</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>hmanabung01@gmail.com</t>
+          <t>vonnelariunaung77560@gmail.com</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="H80" t="n">
+        <v>170</v>
+      </c>
+      <c r="I80" t="n">
+        <v>4</v>
+      </c>
+      <c r="J80" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="K80" t="n">
+        <v>3</v>
+      </c>
+      <c r="L80" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="M80" t="n">
+        <v>7</v>
+      </c>
+      <c r="N80" t="n">
+        <v>56</v>
+      </c>
+      <c r="O80" t="n">
+        <v>217.57</v>
+      </c>
+      <c r="P80" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>256.61</v>
+      </c>
+      <c r="R80" t="n">
+        <v>128</v>
+      </c>
+      <c r="S80" t="n">
+        <v>135</v>
+      </c>
+      <c r="T80" t="n">
         <v>211</v>
       </c>
-      <c r="I80" t="n">
-        <v>3</v>
-      </c>
-      <c r="J80" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="K80" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="M80" t="n">
-        <v>4</v>
-      </c>
-      <c r="N80" t="n">
-        <v>97</v>
-      </c>
-      <c r="O80" t="n">
-        <v>193.61</v>
-      </c>
-      <c r="P80" t="n">
-        <v>96</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>198.14</v>
-      </c>
-      <c r="R80" t="n">
-        <v>193</v>
-      </c>
-      <c r="S80" t="n">
-        <v>197</v>
-      </c>
-      <c r="T80" t="n">
-        <v>95</v>
-      </c>
       <c r="U80" t="n">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="X80" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y80" t="n">
         <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
       </c>
       <c r="AD80" t="n">
-        <v>289</v>
+        <v>390</v>
       </c>
       <c r="AE80" t="n">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="AF80" t="n">
-        <v>95</v>
+        <v>213</v>
       </c>
       <c r="AG80" t="n">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI80" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AJ80" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AK80" t="n">
         <v>0</v>
       </c>
       <c r="AL80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM80" t="n">
         <v>0</v>
       </c>
       <c r="AN80" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AO80" t="n">
         <v>0</v>
       </c>
       <c r="AP80" t="n">
-        <v>289</v>
+        <v>390</v>
       </c>
       <c r="AQ80" t="n">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="AR80" t="n">
-        <v>263</v>
+        <v>211</v>
       </c>
       <c r="AS80" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AU80" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AV80" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="81">
@@ -13295,19 +13283,19 @@
         <v>292</v>
       </c>
       <c r="AR81" t="n">
-        <v>313</v>
+        <v>60</v>
       </c>
       <c r="AS81" t="n">
         <v>0</v>
       </c>
       <c r="AT81" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AU81" t="n">
         <v>0</v>
       </c>
       <c r="AV81" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
     </row>
     <row r="82">
@@ -13453,19 +13441,19 @@
         <v>330</v>
       </c>
       <c r="AR82" t="n">
-        <v>385</v>
+        <v>113</v>
       </c>
       <c r="AS82" t="n">
         <v>0</v>
       </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV82" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
     </row>
     <row r="83">
@@ -13611,19 +13599,19 @@
         <v>299</v>
       </c>
       <c r="AR83" t="n">
-        <v>340</v>
+        <v>159</v>
       </c>
       <c r="AS83" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AT83" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="AU83" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AV83" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84">
@@ -13769,19 +13757,19 @@
         <v>316</v>
       </c>
       <c r="AR84" t="n">
-        <v>378</v>
+        <v>111</v>
       </c>
       <c r="AS84" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="AT84" t="n">
         <v>0</v>
       </c>
       <c r="AU84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV84" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="85">
@@ -13927,19 +13915,19 @@
         <v>299</v>
       </c>
       <c r="AR85" t="n">
-        <v>367</v>
+        <v>126</v>
       </c>
       <c r="AS85" t="n">
         <v>0</v>
       </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU85" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV85" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
     </row>
     <row r="86">
@@ -14085,19 +14073,19 @@
         <v>327</v>
       </c>
       <c r="AR86" t="n">
-        <v>367</v>
+        <v>163</v>
       </c>
       <c r="AS86" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AT86" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AU86" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AV86" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
     </row>
     <row r="87">
@@ -14243,19 +14231,19 @@
         <v>278</v>
       </c>
       <c r="AR87" t="n">
-        <v>360</v>
+        <v>146</v>
       </c>
       <c r="AS87" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AT87" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AU87" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AV87" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
     </row>
     <row r="88">
@@ -14401,19 +14389,19 @@
         <v>362</v>
       </c>
       <c r="AR88" t="n">
-        <v>356</v>
+        <v>70</v>
       </c>
       <c r="AS88" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AT88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV88" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
     </row>
     <row r="89">
@@ -14559,19 +14547,19 @@
         <v>333</v>
       </c>
       <c r="AR89" t="n">
-        <v>405</v>
+        <v>167</v>
       </c>
       <c r="AS89" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AT89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU89" t="n">
         <v>2</v>
       </c>
-      <c r="AU89" t="n">
-        <v>0</v>
-      </c>
       <c r="AV89" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
     </row>
     <row r="90">
@@ -14717,19 +14705,19 @@
         <v>239</v>
       </c>
       <c r="AR90" t="n">
-        <v>301</v>
+        <v>51</v>
       </c>
       <c r="AS90" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT90" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AU90" t="n">
         <v>0</v>
       </c>
       <c r="AV90" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91">
@@ -14875,19 +14863,19 @@
         <v>316</v>
       </c>
       <c r="AR91" t="n">
-        <v>399</v>
+        <v>127</v>
       </c>
       <c r="AS91" t="n">
         <v>0</v>
       </c>
       <c r="AT91" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AU91" t="n">
         <v>0</v>
       </c>
       <c r="AV91" t="n">
-        <v>0</v>
+        <v>293</v>
       </c>
     </row>
     <row r="92">
@@ -15033,19 +15021,19 @@
         <v>360</v>
       </c>
       <c r="AR92" t="n">
-        <v>364</v>
+        <v>108</v>
       </c>
       <c r="AS92" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AT92" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AU92" t="n">
         <v>0</v>
       </c>
       <c r="AV92" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
     </row>
     <row r="93">
@@ -15191,19 +15179,19 @@
         <v>381</v>
       </c>
       <c r="AR93" t="n">
-        <v>335</v>
+        <v>42</v>
       </c>
       <c r="AS93" t="n">
         <v>0</v>
       </c>
       <c r="AT93" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AU93" t="n">
         <v>0</v>
       </c>
       <c r="AV93" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
     </row>
     <row r="94">
@@ -15349,10 +15337,10 @@
         <v>278</v>
       </c>
       <c r="AR94" t="n">
-        <v>373</v>
+        <v>164</v>
       </c>
       <c r="AS94" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="AT94" t="n">
         <v>4</v>
@@ -15361,7 +15349,7 @@
         <v>0</v>
       </c>
       <c r="AV94" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
     </row>
     <row r="95">
@@ -15507,19 +15495,19 @@
         <v>382</v>
       </c>
       <c r="AR95" t="n">
-        <v>356</v>
+        <v>47</v>
       </c>
       <c r="AS95" t="n">
         <v>0</v>
       </c>
       <c r="AT95" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AU95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV95" t="n">
-        <v>3</v>
+        <v>325</v>
       </c>
     </row>
     <row r="96">
@@ -15665,19 +15653,19 @@
         <v>366</v>
       </c>
       <c r="AR96" t="n">
-        <v>282</v>
+        <v>30</v>
       </c>
       <c r="AS96" t="n">
         <v>0</v>
       </c>
       <c r="AT96" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="AU96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV96" t="n">
-        <v>1</v>
+        <v>247</v>
       </c>
     </row>
     <row r="97">
@@ -15823,19 +15811,19 @@
         <v>360</v>
       </c>
       <c r="AR97" t="n">
-        <v>378</v>
+        <v>21</v>
       </c>
       <c r="AS97" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="AT97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU97" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AV97" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="98">
@@ -15981,19 +15969,19 @@
         <v>248</v>
       </c>
       <c r="AR98" t="n">
-        <v>367</v>
+        <v>152</v>
       </c>
       <c r="AS98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT98" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="AU98" t="n">
         <v>0</v>
       </c>
       <c r="AV98" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="99">
@@ -16139,19 +16127,19 @@
         <v>347</v>
       </c>
       <c r="AR99" t="n">
-        <v>321</v>
+        <v>87</v>
       </c>
       <c r="AS99" t="n">
         <v>0</v>
       </c>
       <c r="AT99" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV99" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
     </row>
     <row r="100">
@@ -16297,19 +16285,19 @@
         <v>277</v>
       </c>
       <c r="AR100" t="n">
-        <v>343</v>
+        <v>161</v>
       </c>
       <c r="AS100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AT100" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AU100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV100" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="101">
@@ -16455,19 +16443,19 @@
         <v>399</v>
       </c>
       <c r="AR101" t="n">
-        <v>455</v>
+        <v>134</v>
       </c>
       <c r="AS101" t="n">
         <v>0</v>
       </c>
       <c r="AT101" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AU101" t="n">
         <v>0</v>
       </c>
       <c r="AV101" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
     </row>
     <row r="102">
@@ -16498,7 +16486,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16613,19 +16601,19 @@
         <v>318</v>
       </c>
       <c r="AR102" t="n">
-        <v>472</v>
+        <v>192</v>
       </c>
       <c r="AS102" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AT102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU102" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AV102" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
     </row>
     <row r="103">
@@ -16771,19 +16759,19 @@
         <v>427</v>
       </c>
       <c r="AR103" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="AS103" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AT103" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AU103" t="n">
         <v>0</v>
       </c>
       <c r="AV103" t="n">
-        <v>0</v>
+        <v>364</v>
       </c>
     </row>
     <row r="104">
@@ -16814,7 +16802,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16929,19 +16917,19 @@
         <v>296</v>
       </c>
       <c r="AR104" t="n">
-        <v>422</v>
+        <v>139</v>
       </c>
       <c r="AS104" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AT104" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU104" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AV104" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="105">
@@ -16976,49 +16964,49 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H105" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="I105" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J105" t="n">
-        <v>26.95</v>
+        <v>28.67</v>
       </c>
       <c r="K105" t="n">
         <v>11</v>
       </c>
       <c r="L105" t="n">
-        <v>41.26</v>
+        <v>42.27</v>
       </c>
       <c r="M105" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N105" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="O105" t="n">
-        <v>170.27</v>
+        <v>184.24</v>
       </c>
       <c r="P105" t="n">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="Q105" t="n">
-        <v>361.53</v>
+        <v>444.83</v>
       </c>
       <c r="R105" t="n">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="S105" t="n">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T105" t="n">
         <v>87</v>
       </c>
       <c r="U105" t="n">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="V105" t="n">
         <v>16</v>
@@ -17039,22 +17027,22 @@
         <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
       </c>
       <c r="AD105" t="n">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="AE105" t="n">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="AF105" t="n">
         <v>87</v>
       </c>
       <c r="AG105" t="n">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="AH105" t="n">
         <v>16</v>
@@ -17075,31 +17063,31 @@
         <v>0</v>
       </c>
       <c r="AN105" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="AO105" t="n">
         <v>0</v>
       </c>
       <c r="AP105" t="n">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="AQ105" t="n">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="AR105" t="n">
-        <v>391</v>
+        <v>87</v>
       </c>
       <c r="AS105" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AT105" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AU105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV105" t="n">
-        <v>5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="106">
@@ -17245,19 +17233,19 @@
         <v>395</v>
       </c>
       <c r="AR106" t="n">
-        <v>366</v>
+        <v>113</v>
       </c>
       <c r="AS106" t="n">
         <v>1</v>
       </c>
       <c r="AT106" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="AU106" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV106" t="n">
-        <v>11</v>
+        <v>299</v>
       </c>
     </row>
     <row r="107">
@@ -17403,19 +17391,19 @@
         <v>307</v>
       </c>
       <c r="AR107" t="n">
-        <v>322</v>
+        <v>72</v>
       </c>
       <c r="AS107" t="n">
         <v>0</v>
       </c>
       <c r="AT107" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AU107" t="n">
         <v>0</v>
       </c>
       <c r="AV107" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
     </row>
     <row r="108">
@@ -17561,19 +17549,19 @@
         <v>368</v>
       </c>
       <c r="AR108" t="n">
-        <v>324</v>
+        <v>32</v>
       </c>
       <c r="AS108" t="n">
         <v>0</v>
       </c>
       <c r="AT108" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AU108" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV108" t="n">
-        <v>5</v>
+        <v>304</v>
       </c>
     </row>
     <row r="109">
@@ -17719,10 +17707,10 @@
         <v>313</v>
       </c>
       <c r="AR109" t="n">
-        <v>407</v>
+        <v>193</v>
       </c>
       <c r="AS109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT109" t="n">
         <v>2</v>
@@ -17731,7 +17719,7 @@
         <v>0</v>
       </c>
       <c r="AV109" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
     </row>
     <row r="110">
@@ -17877,10 +17865,10 @@
         <v>404</v>
       </c>
       <c r="AR110" t="n">
-        <v>507</v>
+        <v>213</v>
       </c>
       <c r="AS110" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AT110" t="n">
         <v>0</v>
@@ -17889,7 +17877,7 @@
         <v>3</v>
       </c>
       <c r="AV110" t="n">
-        <v>2</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111">
@@ -18035,19 +18023,19 @@
         <v>307</v>
       </c>
       <c r="AR111" t="n">
-        <v>294</v>
+        <v>109</v>
       </c>
       <c r="AS111" t="n">
         <v>0</v>
       </c>
       <c r="AT111" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AU111" t="n">
         <v>0</v>
       </c>
       <c r="AV111" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
     </row>
     <row r="112">
@@ -18193,19 +18181,19 @@
         <v>262</v>
       </c>
       <c r="AR112" t="n">
-        <v>403</v>
+        <v>178</v>
       </c>
       <c r="AS112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV112" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
     </row>
     <row r="113">
@@ -18351,19 +18339,19 @@
         <v>442</v>
       </c>
       <c r="AR113" t="n">
-        <v>362</v>
+        <v>87</v>
       </c>
       <c r="AS113" t="n">
         <v>0</v>
       </c>
       <c r="AT113" t="n">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="AU113" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AV113" t="n">
-        <v>2</v>
+        <v>286</v>
       </c>
     </row>
     <row r="114">
@@ -18509,19 +18497,19 @@
         <v>561</v>
       </c>
       <c r="AR114" t="n">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="AS114" t="n">
         <v>0</v>
       </c>
       <c r="AT114" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AU114" t="n">
         <v>0</v>
       </c>
       <c r="AV114" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
     </row>
     <row r="115">
@@ -18667,19 +18655,19 @@
         <v>271</v>
       </c>
       <c r="AR115" t="n">
-        <v>344</v>
+        <v>162</v>
       </c>
       <c r="AS115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU115" t="n">
         <v>0</v>
       </c>
       <c r="AV115" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="116">
@@ -18825,111 +18813,111 @@
         <v>292</v>
       </c>
       <c r="AR116" t="n">
-        <v>333</v>
+        <v>102</v>
       </c>
       <c r="AS116" t="n">
         <v>0</v>
       </c>
       <c r="AT116" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="AU116" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV116" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>stivfrancois@gmail.com</t>
+          <t>srirahayudurumias@gmail.com</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Fresly Jeica Manangkoda</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>fmanangkoda12@gmail.com</t>
+          <t>hmanabung01@gmail.com</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>(050) TAMAKO</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H117" t="n">
-        <v>315</v>
+        <v>211</v>
       </c>
       <c r="I117" t="n">
         <v>3</v>
       </c>
       <c r="J117" t="n">
-        <v>5.99</v>
+        <v>6.59</v>
       </c>
       <c r="K117" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L117" t="n">
-        <v>15.38</v>
+        <v>1.67</v>
       </c>
       <c r="M117" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N117" t="n">
-        <v>158</v>
+        <v>97</v>
       </c>
       <c r="O117" t="n">
-        <v>318.19</v>
+        <v>193.61</v>
       </c>
       <c r="P117" t="n">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="Q117" t="n">
-        <v>360.42</v>
+        <v>198.14</v>
       </c>
       <c r="R117" t="n">
-        <v>284</v>
+        <v>193</v>
       </c>
       <c r="S117" t="n">
-        <v>294</v>
+        <v>197</v>
       </c>
       <c r="T117" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="U117" t="n">
-        <v>320</v>
+        <v>149</v>
       </c>
       <c r="V117" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W117" t="n">
         <v>0</v>
       </c>
       <c r="X117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y117" t="n">
         <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -18941,31 +18929,31 @@
         <v>0</v>
       </c>
       <c r="AD117" t="n">
-        <v>435</v>
+        <v>289</v>
       </c>
       <c r="AE117" t="n">
-        <v>371</v>
+        <v>194</v>
       </c>
       <c r="AF117" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="AG117" t="n">
-        <v>320</v>
+        <v>149</v>
       </c>
       <c r="AH117" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI117" t="n">
         <v>0</v>
       </c>
       <c r="AJ117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK117" t="n">
         <v>0</v>
       </c>
       <c r="AL117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM117" t="n">
         <v>0</v>
@@ -18977,75 +18965,75 @@
         <v>0</v>
       </c>
       <c r="AP117" t="n">
-        <v>435</v>
+        <v>289</v>
       </c>
       <c r="AQ117" t="n">
-        <v>371</v>
+        <v>194</v>
       </c>
       <c r="AR117" t="n">
-        <v>364</v>
+        <v>95</v>
       </c>
       <c r="AS117" t="n">
         <v>0</v>
       </c>
       <c r="AT117" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AU117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV117" t="n">
-        <v>6</v>
+        <v>149</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>sulastribwnti@gmail.com</t>
+          <t>stivfrancois@gmail.com</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sutrisno Sariang</t>
+          <t>Fresly Jeica Manangkoda</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>sutrisnosariang90@gmail.com</t>
+          <t>fmanangkoda12@gmail.com</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(050) TAMAKO</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H118" t="n">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="I118" t="n">
         <v>3</v>
       </c>
       <c r="J118" t="n">
-        <v>2.28</v>
+        <v>5.99</v>
       </c>
       <c r="K118" t="n">
         <v>7</v>
       </c>
       <c r="L118" t="n">
-        <v>10.86</v>
+        <v>15.38</v>
       </c>
       <c r="M118" t="n">
         <v>10</v>
@@ -19054,28 +19042,28 @@
         <v>158</v>
       </c>
       <c r="O118" t="n">
-        <v>236.78</v>
+        <v>318.19</v>
       </c>
       <c r="P118" t="n">
-        <v>303</v>
+        <v>126</v>
       </c>
       <c r="Q118" t="n">
-        <v>350.08</v>
+        <v>360.42</v>
       </c>
       <c r="R118" t="n">
-        <v>461</v>
+        <v>284</v>
       </c>
       <c r="S118" t="n">
-        <v>471</v>
+        <v>294</v>
       </c>
       <c r="T118" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="U118" t="n">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="V118" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W118" t="n">
         <v>0</v>
@@ -19096,22 +19084,22 @@
         <v>42</v>
       </c>
       <c r="AC118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD118" t="n">
-        <v>537</v>
+        <v>435</v>
       </c>
       <c r="AE118" t="n">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="AF118" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="AG118" t="n">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="AH118" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI118" t="n">
         <v>0</v>
@@ -19132,108 +19120,108 @@
         <v>42</v>
       </c>
       <c r="AO118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP118" t="n">
-        <v>537</v>
+        <v>435</v>
       </c>
       <c r="AQ118" t="n">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="AR118" t="n">
-        <v>378</v>
+        <v>64</v>
       </c>
       <c r="AS118" t="n">
         <v>0</v>
       </c>
       <c r="AT118" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AU118" t="n">
         <v>0</v>
       </c>
       <c r="AV118" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>sunarditamado2@gmail.com</t>
+          <t>sulastribwnti@gmail.com</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Sutrisno Sariang</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>stevenmanoppo36@gmail.com</t>
+          <t>sutrisnosariang90@gmail.com</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="H119" t="n">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="I119" t="n">
+        <v>3</v>
+      </c>
+      <c r="J119" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K119" t="n">
         <v>7</v>
       </c>
-      <c r="J119" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="K119" t="n">
-        <v>2</v>
-      </c>
       <c r="L119" t="n">
-        <v>1.37</v>
+        <v>10.86</v>
       </c>
       <c r="M119" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N119" t="n">
-        <v>270</v>
+        <v>158</v>
       </c>
       <c r="O119" t="n">
-        <v>256.75</v>
+        <v>236.78</v>
       </c>
       <c r="P119" t="n">
-        <v>155</v>
+        <v>303</v>
       </c>
       <c r="Q119" t="n">
-        <v>135.66</v>
+        <v>350.08</v>
       </c>
       <c r="R119" t="n">
-        <v>425</v>
+        <v>461</v>
       </c>
       <c r="S119" t="n">
-        <v>434</v>
+        <v>471</v>
       </c>
       <c r="T119" t="n">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="U119" t="n">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="V119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W119" t="n">
         <v>0</v>
@@ -19245,31 +19233,31 @@
         <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="AC119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD119" t="n">
-        <v>486</v>
+        <v>537</v>
       </c>
       <c r="AE119" t="n">
-        <v>442</v>
+        <v>403</v>
       </c>
       <c r="AF119" t="n">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="AG119" t="n">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="AH119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI119" t="n">
         <v>0</v>
@@ -19281,117 +19269,117 @@
         <v>0</v>
       </c>
       <c r="AL119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM119" t="n">
         <v>0</v>
       </c>
       <c r="AN119" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="AO119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP119" t="n">
-        <v>486</v>
+        <v>537</v>
       </c>
       <c r="AQ119" t="n">
-        <v>442</v>
+        <v>403</v>
       </c>
       <c r="AR119" t="n">
-        <v>420</v>
+        <v>134</v>
       </c>
       <c r="AS119" t="n">
         <v>0</v>
       </c>
       <c r="AT119" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AU119" t="n">
         <v>0</v>
       </c>
       <c r="AV119" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>tangkabiringananti@gmail.com</t>
+          <t>sunarditamado2@gmail.com</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>hmanabung01@gmail.com</t>
+          <t>stevenmanoppo36@gmail.com</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="H120" t="n">
-        <v>373</v>
+        <v>347</v>
       </c>
       <c r="I120" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J120" t="n">
-        <v>5.21</v>
+        <v>6.21</v>
       </c>
       <c r="K120" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L120" t="n">
-        <v>13.25</v>
+        <v>1.37</v>
       </c>
       <c r="M120" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="N120" t="n">
-        <v>62</v>
+        <v>270</v>
       </c>
       <c r="O120" t="n">
-        <v>72.46000000000001</v>
+        <v>256.75</v>
       </c>
       <c r="P120" t="n">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="Q120" t="n">
-        <v>209.07</v>
+        <v>135.66</v>
       </c>
       <c r="R120" t="n">
-        <v>251</v>
+        <v>425</v>
       </c>
       <c r="S120" t="n">
-        <v>268</v>
+        <v>434</v>
       </c>
       <c r="T120" t="n">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="U120" t="n">
-        <v>266</v>
+        <v>378</v>
       </c>
       <c r="V120" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="W120" t="n">
         <v>0</v>
@@ -19403,31 +19391,31 @@
         <v>0</v>
       </c>
       <c r="Z120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>58</v>
+      </c>
+      <c r="AC120" t="n">
         <v>3</v>
       </c>
-      <c r="AA120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB120" t="n">
-        <v>96</v>
-      </c>
-      <c r="AC120" t="n">
-        <v>0</v>
-      </c>
       <c r="AD120" t="n">
-        <v>544</v>
+        <v>486</v>
       </c>
       <c r="AE120" t="n">
-        <v>380</v>
+        <v>442</v>
       </c>
       <c r="AF120" t="n">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="AG120" t="n">
-        <v>266</v>
+        <v>378</v>
       </c>
       <c r="AH120" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AI120" t="n">
         <v>0</v>
@@ -19439,120 +19427,120 @@
         <v>0</v>
       </c>
       <c r="AL120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>58</v>
+      </c>
+      <c r="AO120" t="n">
         <v>3</v>
       </c>
-      <c r="AM120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN120" t="n">
-        <v>96</v>
-      </c>
-      <c r="AO120" t="n">
-        <v>0</v>
-      </c>
       <c r="AP120" t="n">
-        <v>544</v>
+        <v>486</v>
       </c>
       <c r="AQ120" t="n">
-        <v>380</v>
+        <v>442</v>
       </c>
       <c r="AR120" t="n">
-        <v>430</v>
+        <v>44</v>
       </c>
       <c r="AS120" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU120" t="n">
         <v>0</v>
       </c>
       <c r="AV120" t="n">
-        <v>0</v>
+        <v>378</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>tangkabiringanayen70@gmail.com</t>
+          <t>tangkabiringananti@gmail.com</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>georgemulersasiangsasiang@gmail.com</t>
+          <t>hmanabung01@gmail.com</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>178</v>
+        <v>23</v>
       </c>
       <c r="H121" t="n">
-        <v>63</v>
+        <v>373</v>
       </c>
       <c r="I121" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="J121" t="n">
-        <v>44.14</v>
+        <v>5.21</v>
       </c>
       <c r="K121" t="n">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="L121" t="n">
-        <v>74.17999999999999</v>
+        <v>13.25</v>
       </c>
       <c r="M121" t="n">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="N121" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="O121" t="n">
-        <v>71.81999999999999</v>
+        <v>72.46000000000001</v>
       </c>
       <c r="P121" t="n">
-        <v>48</v>
+        <v>189</v>
       </c>
       <c r="Q121" t="n">
-        <v>109.85</v>
+        <v>209.07</v>
       </c>
       <c r="R121" t="n">
-        <v>81</v>
+        <v>251</v>
       </c>
       <c r="S121" t="n">
-        <v>199</v>
+        <v>268</v>
       </c>
       <c r="T121" t="n">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="U121" t="n">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="V121" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="W121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X121" t="n">
         <v>0</v>
@@ -19561,34 +19549,34 @@
         <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="AC121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD121" t="n">
-        <v>479</v>
+        <v>544</v>
       </c>
       <c r="AE121" t="n">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="AF121" t="n">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="AG121" t="n">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="AH121" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AI121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ121" t="n">
         <v>0</v>
@@ -19597,156 +19585,156 @@
         <v>0</v>
       </c>
       <c r="AL121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM121" t="n">
         <v>0</v>
       </c>
       <c r="AN121" t="n">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="AO121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP121" t="n">
-        <v>479</v>
+        <v>544</v>
       </c>
       <c r="AQ121" t="n">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="AR121" t="n">
-        <v>379</v>
+        <v>164</v>
       </c>
       <c r="AS121" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AU121" t="n">
         <v>0</v>
       </c>
       <c r="AV121" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>tentangsangihe@gmail.com</t>
+          <t>tangkabiringanayen70@gmail.com</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>hmanabung01@gmail.com</t>
+          <t>georgemulersasiangsasiang@gmail.com</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="H122" t="n">
-        <v>367</v>
+        <v>63</v>
       </c>
       <c r="I122" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="J122" t="n">
-        <v>25.44</v>
+        <v>44.14</v>
       </c>
       <c r="K122" t="n">
+        <v>79</v>
+      </c>
+      <c r="L122" t="n">
+        <v>74.17999999999999</v>
+      </c>
+      <c r="M122" t="n">
+        <v>118</v>
+      </c>
+      <c r="N122" t="n">
+        <v>33</v>
+      </c>
+      <c r="O122" t="n">
+        <v>71.81999999999999</v>
+      </c>
+      <c r="P122" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="R122" t="n">
+        <v>81</v>
+      </c>
+      <c r="S122" t="n">
+        <v>199</v>
+      </c>
+      <c r="T122" t="n">
+        <v>185</v>
+      </c>
+      <c r="U122" t="n">
+        <v>242</v>
+      </c>
+      <c r="V122" t="n">
+        <v>6</v>
+      </c>
+      <c r="W122" t="n">
         <v>2</v>
       </c>
-      <c r="L122" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="M122" t="n">
-        <v>18</v>
-      </c>
-      <c r="N122" t="n">
-        <v>191</v>
-      </c>
-      <c r="O122" t="n">
-        <v>248.99</v>
-      </c>
-      <c r="P122" t="n">
-        <v>83</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>123.27</v>
-      </c>
-      <c r="R122" t="n">
-        <v>274</v>
-      </c>
-      <c r="S122" t="n">
+      <c r="X122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>43</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>479</v>
+      </c>
+      <c r="AE122" t="n">
         <v>292</v>
       </c>
-      <c r="T122" t="n">
-        <v>126</v>
-      </c>
-      <c r="U122" t="n">
-        <v>256</v>
-      </c>
-      <c r="V122" t="n">
-        <v>16</v>
-      </c>
-      <c r="W122" t="n">
-        <v>0</v>
-      </c>
-      <c r="X122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z122" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB122" t="n">
-        <v>86</v>
-      </c>
-      <c r="AC122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD122" t="n">
-        <v>485</v>
-      </c>
-      <c r="AE122" t="n">
-        <v>359</v>
-      </c>
       <c r="AF122" t="n">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="AG122" t="n">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="AH122" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AI122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ122" t="n">
         <v>0</v>
@@ -19755,216 +19743,216 @@
         <v>0</v>
       </c>
       <c r="AL122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM122" t="n">
         <v>0</v>
       </c>
       <c r="AN122" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="AO122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP122" t="n">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="AQ122" t="n">
-        <v>359</v>
+        <v>292</v>
       </c>
       <c r="AR122" t="n">
-        <v>419</v>
+        <v>185</v>
       </c>
       <c r="AS122" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AT122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU122" t="n">
         <v>0</v>
       </c>
       <c r="AV122" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>tianfirnanda16@gmail.com</t>
+          <t>tentangsangihe@gmail.com</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>vonnelariunaung77560@gmail.com</t>
+          <t>hmanabung01@gmail.com</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="H123" t="n">
-        <v>198</v>
+        <v>367</v>
       </c>
       <c r="I123" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J123" t="n">
-        <v>44.45</v>
+        <v>25.44</v>
       </c>
       <c r="K123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L123" t="n">
-        <v>5.88</v>
+        <v>2.3</v>
       </c>
       <c r="M123" t="n">
+        <v>18</v>
+      </c>
+      <c r="N123" t="n">
+        <v>191</v>
+      </c>
+      <c r="O123" t="n">
+        <v>248.99</v>
+      </c>
+      <c r="P123" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>123.27</v>
+      </c>
+      <c r="R123" t="n">
+        <v>274</v>
+      </c>
+      <c r="S123" t="n">
+        <v>292</v>
+      </c>
+      <c r="T123" t="n">
+        <v>126</v>
+      </c>
+      <c r="U123" t="n">
+        <v>256</v>
+      </c>
+      <c r="V123" t="n">
         <v>16</v>
       </c>
-      <c r="N123" t="n">
-        <v>136</v>
-      </c>
-      <c r="O123" t="n">
-        <v>435.97</v>
-      </c>
-      <c r="P123" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>213.67</v>
-      </c>
-      <c r="R123" t="n">
-        <v>180</v>
-      </c>
-      <c r="S123" t="n">
-        <v>196</v>
-      </c>
-      <c r="T123" t="n">
-        <v>97</v>
-      </c>
-      <c r="U123" t="n">
-        <v>338</v>
-      </c>
-      <c r="V123" t="n">
-        <v>0</v>
-      </c>
       <c r="W123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y123" t="n">
         <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="AC123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD123" t="n">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="AE123" t="n">
-        <v>398</v>
+        <v>359</v>
       </c>
       <c r="AF123" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="AG123" t="n">
-        <v>338</v>
+        <v>256</v>
       </c>
       <c r="AH123" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK123" t="n">
         <v>0</v>
       </c>
       <c r="AL123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM123" t="n">
         <v>0</v>
       </c>
       <c r="AN123" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="AO123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP123" t="n">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="AQ123" t="n">
-        <v>398</v>
+        <v>359</v>
       </c>
       <c r="AR123" t="n">
-        <v>432</v>
+        <v>126</v>
       </c>
       <c r="AS123" t="n">
         <v>0</v>
       </c>
       <c r="AT123" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AU123" t="n">
         <v>0</v>
       </c>
       <c r="AV123" t="n">
-        <v>3</v>
+        <v>256</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>tikamustika1704@gmail.com</t>
+          <t>tianfirnanda16@gmail.com</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>jeniemonok7@gmail.com</t>
+          <t>vonnelariunaung77560@gmail.com</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -19978,58 +19966,58 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="H124" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="I124" t="n">
+        <v>18</v>
+      </c>
+      <c r="J124" t="n">
+        <v>69.45</v>
+      </c>
+      <c r="K124" t="n">
+        <v>3</v>
+      </c>
+      <c r="L124" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="M124" t="n">
+        <v>21</v>
+      </c>
+      <c r="N124" t="n">
+        <v>100</v>
+      </c>
+      <c r="O124" t="n">
+        <v>339.11</v>
+      </c>
+      <c r="P124" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>168.86</v>
+      </c>
+      <c r="R124" t="n">
+        <v>128</v>
+      </c>
+      <c r="S124" t="n">
+        <v>149</v>
+      </c>
+      <c r="T124" t="n">
+        <v>128</v>
+      </c>
+      <c r="U124" t="n">
+        <v>332</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" t="n">
         <v>7</v>
       </c>
-      <c r="J124" t="n">
-        <v>10.81</v>
-      </c>
-      <c r="K124" t="n">
-        <v>18</v>
-      </c>
-      <c r="L124" t="n">
-        <v>28.21</v>
-      </c>
-      <c r="M124" t="n">
-        <v>25</v>
-      </c>
-      <c r="N124" t="n">
-        <v>72</v>
-      </c>
-      <c r="O124" t="n">
-        <v>123.49</v>
-      </c>
-      <c r="P124" t="n">
-        <v>151</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>237.5</v>
-      </c>
-      <c r="R124" t="n">
-        <v>223</v>
-      </c>
-      <c r="S124" t="n">
-        <v>248</v>
-      </c>
-      <c r="T124" t="n">
-        <v>141</v>
-      </c>
-      <c r="U124" t="n">
-        <v>326</v>
-      </c>
-      <c r="V124" t="n">
-        <v>0</v>
-      </c>
-      <c r="W124" t="n">
-        <v>2</v>
-      </c>
       <c r="X124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y124" t="n">
         <v>0</v>
@@ -20041,31 +20029,31 @@
         <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="AC124" t="n">
         <v>1</v>
       </c>
       <c r="AD124" t="n">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="AE124" t="n">
         <v>371</v>
       </c>
       <c r="AF124" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="AG124" t="n">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="AH124" t="n">
         <v>0</v>
       </c>
       <c r="AI124" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AJ124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK124" t="n">
         <v>0</v>
@@ -20077,114 +20065,114 @@
         <v>0</v>
       </c>
       <c r="AN124" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="AO124" t="n">
         <v>1</v>
       </c>
       <c r="AP124" t="n">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="AQ124" t="n">
         <v>371</v>
       </c>
       <c r="AR124" t="n">
-        <v>437</v>
+        <v>128</v>
       </c>
       <c r="AS124" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AT124" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV124" t="n">
-        <v>0</v>
+        <v>332</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Kristia Mirnawati Tumpias</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>tumpiask@gmail.com</t>
+          <t>tikamustika1704@gmail.com</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>stevenmanoppo36@gmail.com</t>
+          <t>jeniemonok7@gmail.com</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="H125" t="n">
-        <v>295</v>
+        <v>145</v>
       </c>
       <c r="I125" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J125" t="n">
-        <v>11.74</v>
+        <v>10.81</v>
       </c>
       <c r="K125" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="L125" t="n">
-        <v>3.42</v>
+        <v>28.21</v>
       </c>
       <c r="M125" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="N125" t="n">
-        <v>200</v>
+        <v>72</v>
       </c>
       <c r="O125" t="n">
-        <v>162.88</v>
+        <v>123.49</v>
       </c>
       <c r="P125" t="n">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="Q125" t="n">
-        <v>121.96</v>
+        <v>237.5</v>
       </c>
       <c r="R125" t="n">
-        <v>361</v>
+        <v>223</v>
       </c>
       <c r="S125" t="n">
-        <v>382</v>
+        <v>248</v>
       </c>
       <c r="T125" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="U125" t="n">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="V125" t="n">
         <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X125" t="n">
         <v>0</v>
@@ -20193,475 +20181,475 @@
         <v>0</v>
       </c>
       <c r="Z125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>514</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>371</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>141</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>326</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI125" t="n">
         <v>2</v>
       </c>
-      <c r="AA125" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB125" t="n">
-        <v>79</v>
-      </c>
-      <c r="AC125" t="n">
+      <c r="AJ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>514</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>371</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>141</v>
+      </c>
+      <c r="AS125" t="n">
         <v>2</v>
       </c>
-      <c r="AD125" t="n">
-        <v>372</v>
-      </c>
-      <c r="AE125" t="n">
-        <v>372</v>
-      </c>
-      <c r="AF125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG125" t="n">
-        <v>288</v>
-      </c>
-      <c r="AH125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL125" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM125" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN125" t="n">
-        <v>79</v>
-      </c>
-      <c r="AO125" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP125" t="n">
-        <v>372</v>
-      </c>
-      <c r="AQ125" t="n">
-        <v>372</v>
-      </c>
-      <c r="AR125" t="n">
-        <v>303</v>
-      </c>
-      <c r="AS125" t="n">
-        <v>0</v>
-      </c>
       <c r="AT125" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AU125" t="n">
         <v>0</v>
       </c>
       <c r="AV125" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Kristia Mirnawati Tumpias</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ungkealbert39@gmail.com</t>
+          <t>tumpiask@gmail.com</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ferdinandtangkabiringan@gmail.com</t>
+          <t>stevenmanoppo36@gmail.com</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H126" t="n">
-        <v>126</v>
+        <v>295</v>
       </c>
       <c r="I126" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="J126" t="n">
-        <v>8.5</v>
+        <v>11.74</v>
       </c>
       <c r="K126" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L126" t="n">
-        <v>56.54</v>
+        <v>3.42</v>
       </c>
       <c r="M126" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="N126" t="n">
-        <v>74</v>
+        <v>200</v>
       </c>
       <c r="O126" t="n">
-        <v>277.05</v>
+        <v>162.88</v>
       </c>
       <c r="P126" t="n">
-        <v>49</v>
+        <v>161</v>
       </c>
       <c r="Q126" t="n">
-        <v>157.91</v>
+        <v>121.96</v>
       </c>
       <c r="R126" t="n">
-        <v>123</v>
+        <v>361</v>
       </c>
       <c r="S126" t="n">
-        <v>138</v>
+        <v>382</v>
       </c>
       <c r="T126" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="U126" t="n">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="V126" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" t="n">
         <v>2</v>
       </c>
-      <c r="W126" t="n">
-        <v>0</v>
-      </c>
-      <c r="X126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z126" t="n">
-        <v>1</v>
-      </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB126" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="AC126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD126" t="n">
-        <v>441</v>
+        <v>372</v>
       </c>
       <c r="AE126" t="n">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="AF126" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AG126" t="n">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="AH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL126" t="n">
         <v>2</v>
       </c>
-      <c r="AI126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL126" t="n">
-        <v>1</v>
-      </c>
       <c r="AM126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN126" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="AO126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP126" t="n">
-        <v>441</v>
+        <v>372</v>
       </c>
       <c r="AQ126" t="n">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="AR126" t="n">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="AS126" t="n">
         <v>0</v>
       </c>
       <c r="AT126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU126" t="n">
         <v>0</v>
       </c>
       <c r="AV126" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>verawaticristylolaroh02@gmail.com</t>
+          <t>ungkealbert39@gmail.com</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>jeniemonok7@gmail.com</t>
+          <t>ferdinandtangkabiringan@gmail.com</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="H127" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I127" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J127" t="n">
-        <v>7.74</v>
+        <v>8.5</v>
       </c>
       <c r="K127" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L127" t="n">
-        <v>30.84</v>
+        <v>56.54</v>
       </c>
       <c r="M127" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N127" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="O127" t="n">
-        <v>140.67</v>
+        <v>277.05</v>
       </c>
       <c r="P127" t="n">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="Q127" t="n">
-        <v>320.74</v>
+        <v>157.91</v>
       </c>
       <c r="R127" t="n">
-        <v>203</v>
+        <v>123</v>
       </c>
       <c r="S127" t="n">
-        <v>222</v>
+        <v>138</v>
       </c>
       <c r="T127" t="n">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="U127" t="n">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="V127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W127" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="X127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y127" t="n">
         <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="AC127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD127" t="n">
-        <v>505</v>
+        <v>441</v>
       </c>
       <c r="AE127" t="n">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AF127" t="n">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AG127" t="n">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="AH127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI127" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AJ127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK127" t="n">
         <v>0</v>
       </c>
       <c r="AL127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM127" t="n">
         <v>0</v>
       </c>
       <c r="AN127" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="AO127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP127" t="n">
-        <v>505</v>
+        <v>441</v>
       </c>
       <c r="AQ127" t="n">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AR127" t="n">
-        <v>394</v>
+        <v>101</v>
       </c>
       <c r="AS127" t="n">
         <v>0</v>
       </c>
       <c r="AT127" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AU127" t="n">
         <v>0</v>
       </c>
       <c r="AV127" t="n">
-        <v>1</v>
+        <v>306</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>wenaserin@gmail.com</t>
+          <t>verawaticristylolaroh02@gmail.com</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>georgemulersasiangsasiang@gmail.com</t>
+          <t>jeniemonok7@gmail.com</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H128" t="n">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="I128" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J128" t="n">
-        <v>39.08</v>
+        <v>7.74</v>
       </c>
       <c r="K128" t="n">
+        <v>14</v>
+      </c>
+      <c r="L128" t="n">
+        <v>30.84</v>
+      </c>
+      <c r="M128" t="n">
         <v>19</v>
       </c>
-      <c r="L128" t="n">
-        <v>67.73999999999999</v>
-      </c>
-      <c r="M128" t="n">
-        <v>29</v>
-      </c>
       <c r="N128" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="O128" t="n">
-        <v>128.69</v>
+        <v>140.67</v>
       </c>
       <c r="P128" t="n">
-        <v>52</v>
+        <v>142</v>
       </c>
       <c r="Q128" t="n">
-        <v>164.48</v>
+        <v>320.74</v>
       </c>
       <c r="R128" t="n">
-        <v>95</v>
+        <v>203</v>
       </c>
       <c r="S128" t="n">
-        <v>124</v>
+        <v>222</v>
       </c>
       <c r="T128" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="U128" t="n">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="V128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W128" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="X128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y128" t="n">
         <v>0</v>
@@ -20673,31 +20661,31 @@
         <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
       </c>
       <c r="AD128" t="n">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="AE128" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AF128" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="AG128" t="n">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="AH128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AI128" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="AJ128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AK128" t="n">
         <v>0</v>
@@ -20709,118 +20697,118 @@
         <v>0</v>
       </c>
       <c r="AN128" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="AO128" t="n">
         <v>0</v>
       </c>
       <c r="AP128" t="n">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="AQ128" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AR128" t="n">
-        <v>372</v>
+        <v>142</v>
       </c>
       <c r="AS128" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AT128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU128" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV128" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>windametia67@gmail.com</t>
+          <t>wenaserin@gmail.com</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Jeferson Manahampi</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>manahampijeferson94@gmail.com</t>
+          <t>georgemulersasiangsasiang@gmail.com</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="H129" t="n">
-        <v>366</v>
+        <v>90</v>
       </c>
       <c r="I129" t="n">
+        <v>10</v>
+      </c>
+      <c r="J129" t="n">
+        <v>39.08</v>
+      </c>
+      <c r="K129" t="n">
+        <v>19</v>
+      </c>
+      <c r="L129" t="n">
+        <v>67.73999999999999</v>
+      </c>
+      <c r="M129" t="n">
+        <v>29</v>
+      </c>
+      <c r="N129" t="n">
+        <v>43</v>
+      </c>
+      <c r="O129" t="n">
+        <v>128.69</v>
+      </c>
+      <c r="P129" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>164.48</v>
+      </c>
+      <c r="R129" t="n">
+        <v>95</v>
+      </c>
+      <c r="S129" t="n">
+        <v>124</v>
+      </c>
+      <c r="T129" t="n">
+        <v>131</v>
+      </c>
+      <c r="U129" t="n">
+        <v>317</v>
+      </c>
+      <c r="V129" t="n">
         <v>5</v>
       </c>
-      <c r="J129" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="K129" t="n">
+      <c r="W129" t="n">
+        <v>13</v>
+      </c>
+      <c r="X129" t="n">
         <v>2</v>
       </c>
-      <c r="L129" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="M129" t="n">
-        <v>7</v>
-      </c>
-      <c r="N129" t="n">
-        <v>153</v>
-      </c>
-      <c r="O129" t="n">
-        <v>234.39</v>
-      </c>
-      <c r="P129" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>155.02</v>
-      </c>
-      <c r="R129" t="n">
-        <v>257</v>
-      </c>
-      <c r="S129" t="n">
-        <v>264</v>
-      </c>
-      <c r="T129" t="n">
-        <v>59</v>
-      </c>
-      <c r="U129" t="n">
-        <v>187</v>
-      </c>
-      <c r="V129" t="n">
-        <v>9</v>
-      </c>
-      <c r="W129" t="n">
-        <v>0</v>
-      </c>
-      <c r="X129" t="n">
-        <v>3</v>
-      </c>
       <c r="Y129" t="n">
         <v>0</v>
       </c>
@@ -20831,88 +20819,88 @@
         <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="AC129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD129" t="n">
-        <v>360</v>
+        <v>481</v>
       </c>
       <c r="AE129" t="n">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="AF129" t="n">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="AG129" t="n">
-        <v>189</v>
+        <v>317</v>
       </c>
       <c r="AH129" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AI129" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK129" t="n">
         <v>0</v>
       </c>
       <c r="AL129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM129" t="n">
         <v>0</v>
       </c>
       <c r="AN129" t="n">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="AO129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP129" t="n">
-        <v>360</v>
+        <v>481</v>
       </c>
       <c r="AQ129" t="n">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="AR129" t="n">
-        <v>313</v>
+        <v>131</v>
       </c>
       <c r="AS129" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AT129" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AU129" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV129" t="n">
-        <v>1</v>
+        <v>317</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ybawembang@gmail.com</t>
+          <t>windametia67@gmail.com</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Jeferson Manahampi</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>stevenmanoppo36@gmail.com</t>
+          <t>manahampijeferson94@gmail.com</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -20926,58 +20914,58 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="H130" t="n">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="I130" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="J130" t="n">
-        <v>55.32</v>
+        <v>8.4</v>
       </c>
       <c r="K130" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L130" t="n">
-        <v>25.12</v>
+        <v>2.2</v>
       </c>
       <c r="M130" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="N130" t="n">
-        <v>230</v>
+        <v>153</v>
       </c>
       <c r="O130" t="n">
-        <v>289.88</v>
+        <v>234.39</v>
       </c>
       <c r="P130" t="n">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="Q130" t="n">
-        <v>29.68</v>
+        <v>155.02</v>
       </c>
       <c r="R130" t="n">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="S130" t="n">
-        <v>297</v>
+        <v>264</v>
       </c>
       <c r="T130" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="U130" t="n">
-        <v>307</v>
+        <v>187</v>
       </c>
       <c r="V130" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W130" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="X130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y130" t="n">
         <v>0</v>
@@ -20989,28 +20977,28 @@
         <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="AC130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD130" t="n">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="AE130" t="n">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="AF130" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AG130" t="n">
-        <v>307</v>
+        <v>189</v>
       </c>
       <c r="AH130" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AI130" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="AJ130" t="n">
         <v>0</v>
@@ -21019,120 +21007,120 @@
         <v>0</v>
       </c>
       <c r="AL130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM130" t="n">
         <v>0</v>
       </c>
       <c r="AN130" t="n">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="AO130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP130" t="n">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="AQ130" t="n">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="AR130" t="n">
-        <v>386</v>
+        <v>59</v>
       </c>
       <c r="AS130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT130" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AU130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV130" t="n">
-        <v>1</v>
+        <v>187</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>yudhistiratangkabiringan@gmail.com</t>
+          <t>ybawembang@gmail.com</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ferdinandtangkabiringan@gmail.com</t>
+          <t>stevenmanoppo36@gmail.com</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="H131" t="n">
-        <v>221</v>
+        <v>373</v>
       </c>
       <c r="I131" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="J131" t="n">
-        <v>16.91</v>
+        <v>55.32</v>
       </c>
       <c r="K131" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L131" t="n">
-        <v>13.53</v>
+        <v>25.12</v>
       </c>
       <c r="M131" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="N131" t="n">
-        <v>82</v>
+        <v>230</v>
       </c>
       <c r="O131" t="n">
-        <v>251.59</v>
+        <v>289.88</v>
       </c>
       <c r="P131" t="n">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="Q131" t="n">
-        <v>217.97</v>
+        <v>29.68</v>
       </c>
       <c r="R131" t="n">
-        <v>152</v>
+        <v>251</v>
       </c>
       <c r="S131" t="n">
-        <v>161</v>
+        <v>297</v>
       </c>
       <c r="T131" t="n">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="U131" t="n">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="V131" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W131" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="X131" t="n">
         <v>0</v>
@@ -21147,28 +21135,28 @@
         <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AC131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD131" t="n">
-        <v>400</v>
+        <v>447</v>
       </c>
       <c r="AE131" t="n">
-        <v>261</v>
+        <v>334</v>
       </c>
       <c r="AF131" t="n">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="AG131" t="n">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="AH131" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AI131" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AJ131" t="n">
         <v>0</v>
@@ -21183,189 +21171,347 @@
         <v>0</v>
       </c>
       <c r="AN131" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AO131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP131" t="n">
-        <v>400</v>
+        <v>447</v>
       </c>
       <c r="AQ131" t="n">
-        <v>261</v>
+        <v>334</v>
       </c>
       <c r="AR131" t="n">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="AS131" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="AT131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="n">
         <v>0</v>
       </c>
       <c r="AV131" t="n">
-        <v>0</v>
+        <v>307</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>yustindurian@gmail.com</t>
+          <t>yudhistiratangkabiringan@gmail.com</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>fianemansauda89@gmail.com</t>
+          <t>ferdinandtangkabiringan@gmail.com</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>(070) TABUKAN TENGAH</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H132" t="n">
-        <v>397</v>
+        <v>221</v>
       </c>
       <c r="I132" t="n">
         <v>5</v>
       </c>
       <c r="J132" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="K132" t="n">
+        <v>4</v>
+      </c>
+      <c r="L132" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="M132" t="n">
+        <v>9</v>
+      </c>
+      <c r="N132" t="n">
+        <v>82</v>
+      </c>
+      <c r="O132" t="n">
+        <v>251.59</v>
+      </c>
+      <c r="P132" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>217.97</v>
+      </c>
+      <c r="R132" t="n">
+        <v>152</v>
+      </c>
+      <c r="S132" t="n">
+        <v>161</v>
+      </c>
+      <c r="T132" t="n">
+        <v>139</v>
+      </c>
+      <c r="U132" t="n">
+        <v>209</v>
+      </c>
+      <c r="V132" t="n">
+        <v>6</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>400</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>261</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>139</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>209</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>400</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>261</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>139</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Yustin Durian</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>yustindurian@gmail.com</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Fiane Greti Mansauda</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>fianemansauda89@gmail.com</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>(070) TABUKAN TENGAH</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Kharis</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>24</v>
+      </c>
+      <c r="H133" t="n">
+        <v>397</v>
+      </c>
+      <c r="I133" t="n">
+        <v>5</v>
+      </c>
+      <c r="J133" t="n">
         <v>7.58</v>
       </c>
-      <c r="K132" t="n">
+      <c r="K133" t="n">
         <v>12</v>
       </c>
-      <c r="L132" t="n">
+      <c r="L133" t="n">
         <v>16.22</v>
       </c>
-      <c r="M132" t="n">
+      <c r="M133" t="n">
         <v>17</v>
       </c>
-      <c r="N132" t="n">
+      <c r="N133" t="n">
         <v>151</v>
       </c>
-      <c r="O132" t="n">
+      <c r="O133" t="n">
         <v>254.51</v>
       </c>
-      <c r="P132" t="n">
+      <c r="P133" t="n">
         <v>80</v>
       </c>
-      <c r="Q132" t="n">
+      <c r="Q133" t="n">
         <v>121.68</v>
       </c>
-      <c r="R132" t="n">
+      <c r="R133" t="n">
         <v>231</v>
       </c>
-      <c r="S132" t="n">
+      <c r="S133" t="n">
         <v>248</v>
       </c>
-      <c r="T132" t="n">
+      <c r="T133" t="n">
         <v>131</v>
       </c>
-      <c r="U132" t="n">
+      <c r="U133" t="n">
         <v>278</v>
       </c>
-      <c r="V132" t="n">
+      <c r="V133" t="n">
         <v>2</v>
       </c>
-      <c r="W132" t="n">
-        <v>0</v>
-      </c>
-      <c r="X132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB132" t="n">
+      <c r="W133" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB133" t="n">
         <v>43</v>
       </c>
-      <c r="AC132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD132" t="n">
+      <c r="AC133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD133" t="n">
         <v>456</v>
       </c>
-      <c r="AE132" t="n">
+      <c r="AE133" t="n">
         <v>325</v>
       </c>
-      <c r="AF132" t="n">
+      <c r="AF133" t="n">
         <v>131</v>
       </c>
-      <c r="AG132" t="n">
+      <c r="AG133" t="n">
         <v>278</v>
       </c>
-      <c r="AH132" t="n">
+      <c r="AH133" t="n">
         <v>2</v>
       </c>
-      <c r="AI132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN132" t="n">
+      <c r="AI133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN133" t="n">
         <v>43</v>
       </c>
-      <c r="AO132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP132" t="n">
+      <c r="AO133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP133" t="n">
         <v>456</v>
       </c>
-      <c r="AQ132" t="n">
+      <c r="AQ133" t="n">
         <v>325</v>
       </c>
-      <c r="AR132" t="n">
-        <v>368</v>
-      </c>
-      <c r="AS132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT132" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV132" t="n">
-        <v>0</v>
+      <c r="AR133" t="n">
+        <v>131</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>278</v>
       </c>
     </row>
   </sheetData>
